--- a/singscore_new_code/results/Deep_search_results/deepsearch_3_ADMINISTRATION_regulation_effect_rationale_citation_tab.xlsx
+++ b/singscore_new_code/results/Deep_search_results/deepsearch_3_ADMINISTRATION_regulation_effect_rationale_citation_tab.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GS\PySingscore_replicate\singscore_new_code\results\Deep_search_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1F37D2-D012-4C82-816D-FA2120A17BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7AEFB0-13BC-4520-8724-8AA872FA5B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{114103B9-708B-4BD3-9F98-827A0F030AF4}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="6" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$B$1:$B$48</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4990" uniqueCount="1384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5873" uniqueCount="1502">
   <si>
     <t>Pathway</t>
   </si>
@@ -8366,21 +8369,114 @@
     <t>Dostarlimab</t>
   </si>
   <si>
-    <t>KEGG_JAK_STAT_SIGNALING_PATHWAY</t>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (IFN-γ axis):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Intact IFNγ–JAK1/2–STAT1 signaling in breast tumors supports PD-L1 induction, antigen-presentation and Th1 polarization, predicting better PD-1 responses.</t>
+    <t>REACTOME_CO_INHIBITION_BY_PD_1</t>
+  </si>
+  <si>
+    <t>PMID:17606980; PMID:35064011; PMID:37917058; PMID:33001143; PMID:33278935; PMID:32101663; NCT02715284; NCT02819518; NCT03036488</t>
+  </si>
+  <si>
+    <t>PMID:27433843; PMID:27903500; DOI:10.1186/s40364-020-00212-5</t>
+  </si>
+  <si>
+    <t>PMID:21739672; PMID:24210163</t>
+  </si>
+  <si>
+    <t>PMID:17606980; PMID:21739672</t>
+  </si>
+  <si>
+    <t>PMID:17606980; PMID:30635237; PMID:35064011; PMID:37917058</t>
+  </si>
+  <si>
+    <t>PMID:17606980; PMID:21739672; PMID:27433843</t>
+  </si>
+  <si>
+    <t>PMID:17606980</t>
+  </si>
+  <si>
+    <t>KEGG_T_CELL_RECEPTOR_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>PMID:30635237; PMID:24210163; PMID:21739672</t>
+  </si>
+  <si>
+    <t>PMID:24210163; PMID:21739672; PMID:26205583</t>
+  </si>
+  <si>
+    <t>PMID:24210163; PMID:21739672</t>
+  </si>
+  <si>
+    <t>PMID:24210163</t>
+  </si>
+  <si>
+    <t>PMID:30635237; PMID:26205583</t>
+  </si>
+  <si>
+    <t>PMID:21739672; PMID:26205583</t>
+  </si>
+  <si>
+    <t>PMID:26205583; PMID:21739672</t>
+  </si>
+  <si>
+    <t>PMID:27433843; PMID:35139274</t>
+  </si>
+  <si>
+    <t>PMID:27433843</t>
+  </si>
+  <si>
+    <t>PMID:27433843; PMID:27903500</t>
+  </si>
+  <si>
+    <t>PMID:35139274</t>
+  </si>
+  <si>
+    <t>KEGG_MEDICUS_REFERENCE_CGAS_STING_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>PMID:27707838; PMID:37395684</t>
+  </si>
+  <si>
+    <t>PMID:27707838; DOI:10.1186/s40364-020-00212-5</t>
+  </si>
+  <si>
+    <t>PMID:27707838</t>
+  </si>
+  <si>
+    <t>GOBP_ANTIGEN_PROCESSING_AND_PRESENTATION_OF_PEPTIDE_ANTIGEN_VIA_MHC_CLASS_I</t>
+  </si>
+  <si>
+    <t>PMID:27433843; PMID:29084927; DOI:10.1186/s40364-020-00212-5</t>
+  </si>
+  <si>
+    <t>PMID:27433843; DOI:10.1186/s40364-020-00212-5</t>
+  </si>
+  <si>
+    <t>PMID:27433843; PMID:29084927</t>
+  </si>
+  <si>
+    <t>PMID:29443960; PMID:29669246; PMID:32391193; DOI:10.3389/fimmu.2020.00784</t>
+  </si>
+  <si>
+    <t>PMID:29443960; PMID:29669246</t>
+  </si>
+  <si>
+    <t>PMID:29443960; PMID:29669246; PMID:32391193</t>
+  </si>
+  <si>
+    <t>PMID:29443960; PMID:32391193; PMID:29669246</t>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> High PD-1/PD-L1 signaling on TIL-rich TNBC (inflamed, PD-L1⁺ CPS≥10) indicates a “braked” but pre-existing anti-tumor T-cell response, which is precisely released by PD-1 blockade (class effect; extrapolated from pembrolizumab in TNBC to dostarlimab).</t>
     </r>
   </si>
   <si>
@@ -8395,7 +8491,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Constitutive oncogenic JAK/STAT3 activation can drive tumor survival and immunosuppressive cytokine production, so some JAK-high tumors may still resist PD-1 therapy.</t>
+      <t xml:space="preserve"> Extremely exhausted PD-1^hi TIM-3^⁺/LAG-3^⁺ T cells plus suppressive myeloid cells can make tumors only partially PD-1-dependent; even with high PD-1 signaling, additional checkpoints or metabolic brakes can blunt response.</t>
     </r>
   </si>
   <si>
@@ -8410,7 +8506,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Partial JAK–STAT downregulation in tumor cells but intact in immune cells might still allow systemic IFN responses and benefit from PD-1 blockade.</t>
+      <t xml:space="preserve"> A subset of TNBC may have modest PD-1 signaling but high PD-L1 or other class-I neoantigens plus abundant stem-like PD-1^int TCF1⁺ CD8⁺ T cells that can still be effectively unleashed by PD-1 blockade.</t>
     </r>
   </si>
   <si>
@@ -8425,7 +8521,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Tumors with JAK1/2-loss or STAT1 defects cannot respond to IFN-γ, fail to upregulate MHC I/PD-L1 appropriately and are prototypically resistant to PD-1 blockade.</t>
+      <t xml:space="preserve"> PD-1 co-inhibition is low in “immune-desert” or PD-1–independent TNBC (few TILs, low PD-1/PD-L1), so there is little target for dostarlimab and tumors are primarily resistant.</t>
     </r>
   </si>
   <si>
@@ -8440,7 +8536,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Successful PD-1 blockade increases IFN-γ production, leading to heightened JAK–STAT signaling and a positive feedback loop of antigen-presentation and effector function.</t>
+      <t xml:space="preserve"> Dostarlimab binds PD-1 and blocks SHP2 recruitment, effectively reducing PD-1 co-inhibitory signaling and restoring TCR/CD28 signaling, leading to durable responses in dMMR-like, inflamed breast tumors (by analogy to endometrial and MSI-H tumors).</t>
     </r>
   </si>
   <si>
@@ -8455,22 +8551,37 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Some progressing lesions may retain JAK–STAT activation but have parallel escape (TGF-β/WNT/IDO1), so JAK-STAT “up” does not guarantee sensitivity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically not possible (tumor-intrinsic):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> True loss of JAK–STAT signaling in tumor cells would undermine PD-1-driven immunity; any bulk “down” in responders likely reflects tumor clearance rather than a driver of sensitivity.</t>
+      <t xml:space="preserve"> Even when PD-1 signaling is effectively blocked, tumors may adapt via alternative checkpoints (e.g. TIM-3, TIGIT), stromal exclusion or antigen loss, leading to clinical resistance despite low PD-1 activity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically not possible:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A true increase in functional PD-1 co-inhibition cannot be directly induced by a blocking antibody; any signature-level “up” would reflect more PD-1⁺ T cells entering the tumor but signaling remains blocked, so this does not mechanistically drive sensitivity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate (signature sense):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Non-responding tumors may accumulate highly exhausted PD-1^hi cells plus compensatory PD-L1 or ligand overexpression so that, despite antibody binding, effective downstream co-inhibition persists or is bypassed, manifesting as an “up” signature and clinical resistance.</t>
     </r>
   </si>
   <si>
@@ -8485,104 +8596,38 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Acquisition of JAK1/2 inactivating mutations or negative regulators under PD-1 pressure silences JAK–STAT signaling and is a well-described route to acquired resistance.</t>
-    </r>
-  </si>
-  <si>
-    <t>REACTOME_CO_INHIBITION_BY_PD_1</t>
-  </si>
-  <si>
-    <t>PMID:17606980; PMID:35064011; PMID:37917058; PMID:33001143; PMID:33278935; PMID:32101663; NCT02715284; NCT02819518; NCT03036488</t>
-  </si>
-  <si>
-    <t>PMID:27433843; PMID:27903500; DOI:10.1186/s40364-020-00212-5</t>
-  </si>
-  <si>
-    <t>PMID:21739672; PMID:24210163</t>
-  </si>
-  <si>
-    <t>PMID:17606980; PMID:21739672</t>
-  </si>
-  <si>
-    <t>PMID:17606980; PMID:30635237; PMID:35064011; PMID:37917058</t>
-  </si>
-  <si>
-    <t>PMID:17606980; PMID:21739672; PMID:27433843</t>
-  </si>
-  <si>
-    <t>PMID:17606980</t>
-  </si>
-  <si>
-    <t>KEGG_T_CELL_RECEPTOR_SIGNALING_PATHWAY</t>
-  </si>
-  <si>
-    <t>PMID:30635237; PMID:24210163; PMID:21739672</t>
-  </si>
-  <si>
-    <t>PMID:24210163; PMID:21739672; PMID:26205583</t>
-  </si>
-  <si>
-    <t>PMID:24210163; PMID:21739672</t>
-  </si>
-  <si>
-    <t>PMID:24210163</t>
-  </si>
-  <si>
-    <t>PMID:30635237; PMID:26205583</t>
-  </si>
-  <si>
-    <t>PMID:21739672; PMID:26205583</t>
-  </si>
-  <si>
-    <t>PMID:26205583; PMID:21739672</t>
-  </si>
-  <si>
-    <t>PMID:27433843; PMID:35139274</t>
-  </si>
-  <si>
-    <t>PMID:27433843</t>
-  </si>
-  <si>
-    <t>PMID:27433843; PMID:27903500</t>
-  </si>
-  <si>
-    <t>PMID:35139274</t>
-  </si>
-  <si>
-    <t>KEGG_MEDICUS_REFERENCE_CGAS_STING_SIGNALING_PATHWAY</t>
-  </si>
-  <si>
-    <t>PMID:27707838; PMID:37395684</t>
-  </si>
-  <si>
-    <t>PMID:27707838; DOI:10.1186/s40364-020-00212-5</t>
-  </si>
-  <si>
-    <t>PMID:27707838</t>
-  </si>
-  <si>
-    <t>GOBP_ANTIGEN_PROCESSING_AND_PRESENTATION_OF_PEPTIDE_ANTIGEN_VIA_MHC_CLASS_I</t>
-  </si>
-  <si>
-    <t>PMID:27433843; PMID:29084927; DOI:10.1186/s40364-020-00212-5</t>
-  </si>
-  <si>
-    <t>PMID:27433843; DOI:10.1186/s40364-020-00212-5</t>
-  </si>
-  <si>
-    <t>PMID:27433843; PMID:29084927</t>
-  </si>
-  <si>
-    <t>PMID:29443960; PMID:29669246; PMID:32391193; DOI:10.3389/fimmu.2020.00784</t>
-  </si>
-  <si>
-    <t>PMID:29443960; PMID:29669246</t>
-  </si>
-  <si>
-    <t>PMID:29443960; PMID:29669246; PMID:32391193</t>
-  </si>
-  <si>
-    <t>PMID:29443960; PMID:32391193; PMID:29669246</t>
+      <t xml:space="preserve"> An active but PD-1-restrained TCR program in intratumoral CD8⁺ T cells (high TCR/NFAT/NF-κB gene expression plus PD-1/PD-L1) defines “hot” TNBC that is primed for robust re-activation by PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Some TNBCs show strong TCR activation signatures but are dominated by terminally exhausted or Treg-skewed infiltrates where sustained TCR stimulation without adequate co-stimulation leads to anergy and poor PD-1 benefit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A tumor with low bulk TCR signature but a small pool of stem-like PD-1^int TCF1⁺ cells in draining nodes may still mount an effective response once PD-1 is blocked and cross-priming increases.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -8596,7 +8641,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> High PD-1/PD-L1 signaling on TIL-rich TNBC (inflamed, PD-L1⁺ CPS≥10) indicates a “braked” but pre-existing anti-tumor T-cell response, which is precisely released by PD-1 blockade (class effect; extrapolated from pembrolizumab in TNBC to dostarlimab).</t>
+      <t xml:space="preserve"> Immune-desert or anergic TNBC with weak TCR signaling (few TCR transcripts, low CD3/TCRζ) lacks primed effector cells, so PD-1 blockade alone is unlikely to work.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dostarlimab blocks PD-1, releasing proximal TCR signaling (ZAP70, PI3K, MAPK) so that tumor-specific T cells proliferate and produce IFN-γ, correlating with clinical responses.</t>
     </r>
   </si>
   <si>
@@ -8611,7 +8671,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Extremely exhausted PD-1^hi TIM-3^⁺/LAG-3^⁺ T cells plus suppressive myeloid cells can make tumors only partially PD-1-dependent; even with high PD-1 signaling, additional checkpoints or metabolic brakes can blunt response.</t>
+      <t xml:space="preserve"> Some non-responders show transient TCR activation but rapidly develop counter-regulation (e.g., PD-1–independent anergy or Treg expansion), so an “up” TCR signature doesn’t always translate into tumor control.</t>
     </r>
   </si>
   <si>
@@ -8626,7 +8686,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> A subset of TNBC may have modest PD-1 signaling but high PD-L1 or other class-I neoantigens plus abundant stem-like PD-1^int TCF1⁺ CD8⁺ T cells that can still be effectively unleashed by PD-1 blockade.</t>
+      <t xml:space="preserve"> In highly responsive tumors, rapid tumor clearance and contraction of effector T-cell pool can yield a lower TCR signature at bulk RNA level while the patient remains sensitive/clinical responder.</t>
     </r>
   </si>
   <si>
@@ -8641,7 +8701,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> PD-1 co-inhibition is low in “immune-desert” or PD-1–independent TNBC (few TILs, low PD-1/PD-L1), so there is little target for dostarlimab and tumors are primarily resistant.</t>
+      <t xml:space="preserve"> Failure of TCR re-invigoration (persistent low TCR signaling after treatment) due to intrinsic T-cell defects or dominant suppressive pathways predicts lack of response to PD-1 blockade.</t>
     </r>
   </si>
   <si>
@@ -8656,7 +8716,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Dostarlimab binds PD-1 and blocks SHP2 recruitment, effectively reducing PD-1 co-inhibitory signaling and restoring TCR/CD28 signaling, leading to durable responses in dMMR-like, inflamed breast tumors (by analogy to endometrial and MSI-H tumors).</t>
+      <t xml:space="preserve"> An inflamed IFN-γ gene signature (CXCL9/10, IDO1, HLA genes) in TNBC associates with TILs and better outcomes with PD-1/PD-L1 blockade, indicating pre-existing Th1/CD8⁺ immunity.</t>
     </r>
   </si>
   <si>
@@ -8671,7 +8731,307 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Even when PD-1 signaling is effectively blocked, tumors may adapt via alternative checkpoints (e.g. TIM-3, TIGIT), stromal exclusion or antigen loss, leading to clinical resistance despite low PD-1 activity.</t>
+      <t xml:space="preserve"> Very strong IFN-γ signaling can select for JAK1/2 or B2M mutations, leading to eventual PD-1 resistance despite an initially high IFN signature.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Some TNBCs with modest IFN-γ signatures may still respond when cGAS–STING or neoantigen load is high and quickly induces an IFN-γ program after PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Lack of IFN-γ signaling (low STAT1-inducible genes) indicates poor antigen presentation and is a classic feature of primary PD-1 resistance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Effective PD-1 blockade enhances CD8⁺ effector function, leading to a surge in IFN-γ–responsive transcripts and MHC I/PD-L1 induction, typical of responders.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In some non-responders, persistent IFN-γ may induce strong PD-L1, IDO1 and negative feedback while parallel JAK-STAT lesions in tumor cells blunt antiproliferative effects, yielding radiologic progression.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Once tumors regress, IFN-γ levels and corresponding signatures can normalize despite durable immune memory and ongoing sensitivity to retreatment.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Loss of IFN-γ signaling via JAK1/2 mutations during therapy leads to downregulation of IFN-γ–inducible genes and acquired resistance to PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Breast tumors with active cGAS–STING signaling (dsDNA sensing, type I IFN, chemokines) show higher immune infiltration and are more likely to respond to PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chronic STING activation can drive immunosuppressive myeloid cells or exhaustion, so a high STING signature may occasionally coexist with primary resistance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Low baseline cGAS–STING may still permit response if other innate pathways (e.g. viral STING agonists, RT-induced DNA damage) are activated around the time of PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cGAS–STING–deficient TNBCs are poorly inflamed and lack type I IFN priming, typically rendering PD-1 monotherapy ineffective.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate (combo/indirect):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Radiotherapy or DNA-damaging chemo combined with dostarlimab can activate cGAS–STING, amplifying type I IFN and enhancing PD-1 response in breast cancer models.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Excessive STING activation may induce chronic inflammation with myeloid-dominant, suppressive microenvironments that counteract T-cell reinvigoration.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In deep responders, tumor eradication can reduce tumor DNA and STING engagement, lowering the signature despite maintained clinical sensitivity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tumors may downregulate cGAS or STING during immune editing, extinguishing type I IFN production and leading to secondary resistance to PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> High HLA-I/B2M/TAP expression and antigen-processing signatures in TNBC support efficient presentation of neoantigens to CD8⁺ T cells, favoring response to PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Some tumors with high MHC I still evade via other suppressive mechanisms (e.g. TGF-β, WNT, Tregs), leading to apparent resistance despite intact presentation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Focally reduced MHC I may coexist with strong MHC II and cross-presentation by DCs, allowing PD-1 blockade to work if presentation is restored by IFN-γ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Loss of B2M or defects in TAP/ERAP lead to poor MHC I antigen presentation, a classic cause of primary resistance to PD-1 inhibition.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Successful PD-1 blockade amplifies IFN-γ signaling, increasing MHC I/antigen-processing gene expression and epitope spreading, supporting durable control.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tumors may transiently increase MHC I yet still progress if downstream T cells are exhausted, deleted or excluded.</t>
     </r>
   </si>
   <si>
@@ -8686,22 +9046,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> A true increase in functional PD-1 co-inhibition cannot be directly induced by a blocking antibody; any signature-level “up” would reflect more PD-1⁺ T cells entering the tumor but signaling remains blocked, so this does not mechanistically drive sensitivity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (signature sense):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Non-responding tumors may accumulate highly exhausted PD-1^hi cells plus compensatory PD-L1 or ligand overexpression so that, despite antibody binding, effective downstream co-inhibition persists or is bypassed, manifesting as an “up” signature and clinical resistance.</t>
+      <t xml:space="preserve"> True reduction of antigen presentation in remaining tumor cells would undermine CD8-mediated control; any bulk “down” signature in a responder is more likely due to tumor clearance rather than a mechanism of sensitivity.</t>
     </r>
   </si>
   <si>
@@ -8716,7 +9061,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> An active but PD-1-restrained TCR program in intratumoral CD8⁺ T cells (high TCR/NFAT/NF-κB gene expression plus PD-1/PD-L1) defines “hot” TNBC that is primed for robust re-activation by PD-1 blockade.</t>
+      <t xml:space="preserve"> Under immune pressure from PD-1 blockade, tumors may acquire B2M or HLA lesions, decreasing antigen presentation and causing acquired resistance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> High stromal TGF-β signatures correlate with T-cell exclusion and poor response to PD-1/PD-L1 blockade, including in breast-cancer-like immune-excluded phenotypes.</t>
     </r>
   </si>
   <si>
@@ -8731,7 +9091,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Some TNBCs show strong TCR activation signatures but are dominated by terminally exhausted or Treg-skewed infiltrates where sustained TCR stimulation without adequate co-stimulation leads to anergy and poor PD-1 benefit.</t>
+      <t xml:space="preserve"> A subset of TGF-β-high tumors may still respond if they also harbor very strong neoantigen load/TILs or are treated with combined TGF-β and PD-1 blockade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Low TGF-β signaling reduces stromal exclusion, facilitating T-cell infiltration and better PD-1 responses in inflamed TNBC.</t>
     </r>
   </si>
   <si>
@@ -8746,7 +9121,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> A tumor with low bulk TCR signature but a small pool of stem-like PD-1^int TCF1⁺ cells in draining nodes may still mount an effective response once PD-1 is blocked and cross-priming increases.</t>
+      <t xml:space="preserve"> Resistance despite low TGF-β implies other dominant immune escape mechanisms (e.g., WNT–β-catenin, IDO1), not TGF-β itself.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In responders, transient TGF-β upregulation may occur as negative feedback but generally does not drive sensitivity; durable benefit usually requires TGF-β to remain constrained.</t>
     </r>
   </si>
   <si>
@@ -8761,8 +9151,206 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Immune-desert or anergic TNBC with weak TCR signaling (few TCR transcripts, low CD3/TCRζ) lacks primed effector cells, so PD-1 blockade alone is unlikely to work.</t>
-    </r>
+      <t xml:space="preserve"> Adaptive stromal TGF-β upregulation under PD-1 pressure can harden immune exclusion and drive resistance, motivating anti-TGF-β plus PD-1 combinations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate (combo):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Co-targeting TGF-β or stromal reprogramming with PD-1 blockade reduces TGF-β signaling, re-opens the stroma and enhances T-cell penetration, improving PD-1 efficacy.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically rare:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Persistent resistance despite suppressed TGF-β suggests other escape nodes (e.g., JAK/STAT loss, MHC I loss, WNT activation).</t>
+    </r>
+  </si>
+  <si>
+    <t>Elacestrant</t>
+  </si>
+  <si>
+    <t>Drug / Class</t>
+  </si>
+  <si>
+    <t>Category for your schema</t>
+  </si>
+  <si>
+    <t>Short note</t>
+  </si>
+  <si>
+    <t>Small molecule inhibitor</t>
+  </si>
+  <si>
+    <t>CDK4/6 inhibitor</t>
+  </si>
+  <si>
+    <t>PI3Kα inhibitor</t>
+  </si>
+  <si>
+    <t>Non-steroidal aromatase inhibitor</t>
+  </si>
+  <si>
+    <t>Monoclonal antibody</t>
+  </si>
+  <si>
+    <t>Anti-PD-L1 mAb</t>
+  </si>
+  <si>
+    <t>Anti-VEGF-A mAb</t>
+  </si>
+  <si>
+    <t>AKT inhibitor</t>
+  </si>
+  <si>
+    <t>Anti-PD-1 mAb</t>
+  </si>
+  <si>
+    <t>Oral SERD</t>
+  </si>
+  <si>
+    <t>Entrectinib</t>
+  </si>
+  <si>
+    <t>TRK/ROS1/ALK inhibitor</t>
+  </si>
+  <si>
+    <t>Everolimus</t>
+  </si>
+  <si>
+    <t>mTOR inhibitor</t>
+  </si>
+  <si>
+    <t>Exemestane</t>
+  </si>
+  <si>
+    <t>Steroidal aromatase inhibitor</t>
+  </si>
+  <si>
+    <t>Fulvestrant</t>
+  </si>
+  <si>
+    <t>Injectable SERD (non-antibody small molecule)</t>
+  </si>
+  <si>
+    <t>Lapatinib</t>
+  </si>
+  <si>
+    <t>HER2/EGFR TKI</t>
+  </si>
+  <si>
+    <t>Larotrectinib</t>
+  </si>
+  <si>
+    <t>TRK inhibitor</t>
+  </si>
+  <si>
+    <t>Letrozole</t>
+  </si>
+  <si>
+    <t>Margetuximab</t>
+  </si>
+  <si>
+    <t>Fc-engineered anti-HER2 mAb</t>
+  </si>
+  <si>
+    <t>Neratinib</t>
+  </si>
+  <si>
+    <t>Irreversible pan-HER TKI</t>
+  </si>
+  <si>
+    <t>Olaparib</t>
+  </si>
+  <si>
+    <t>PARP inhibitor</t>
+  </si>
+  <si>
+    <t>Microtubule-stabilizing cytotoxic</t>
+  </si>
+  <si>
+    <t>Palbociclib</t>
+  </si>
+  <si>
+    <t>Pembrolizumab</t>
+  </si>
+  <si>
+    <t>Pertuzumab</t>
+  </si>
+  <si>
+    <t>Anti-HER2 dimerization mAb</t>
+  </si>
+  <si>
+    <t>Ribociclib</t>
+  </si>
+  <si>
+    <t>Sacituzumab govitecan</t>
+  </si>
+  <si>
+    <t>Monoclonal antibody*</t>
+  </si>
+  <si>
+    <t>ADC: Trop-2 mAb + SN-38 payload (*antibody-based)</t>
+  </si>
+  <si>
+    <t>Selpercatinib</t>
+  </si>
+  <si>
+    <t>RET inhibitor</t>
+  </si>
+  <si>
+    <t>Talazoparib</t>
+  </si>
+  <si>
+    <t>Tamoxifen</t>
+  </si>
+  <si>
+    <t>SERM</t>
+  </si>
+  <si>
+    <t>Toremifene</t>
+  </si>
+  <si>
+    <t>Trastuzumab</t>
+  </si>
+  <si>
+    <t>Anti-HER2 mAb</t>
+  </si>
+  <si>
+    <t>Trastuzumab deruxtecan</t>
+  </si>
+  <si>
+    <t>ADC: HER2 mAb + deruxtecan payload (*antibody-based)</t>
+  </si>
+  <si>
+    <t>Trastuzumab emtansine (T-DM1)</t>
+  </si>
+  <si>
+    <t>ADC: HER2 mAb + DM1 payload (*antibody-based)</t>
+  </si>
+  <si>
+    <t>Tucatinib</t>
+  </si>
+  <si>
+    <t>HER2-selective TKI</t>
   </si>
   <si>
     <r>
@@ -8776,8 +9364,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Dostarlimab blocks PD-1, releasing proximal TCR signaling (ZAP70, PI3K, MAPK) so that tumor-specific T cells proliferate and produce IFN-γ, correlating with clinical responses.</t>
-    </r>
+      <t xml:space="preserve"> High HALLMARK_ESTROGEN_RESPONSE_EARLY in ER+/HER2− luminal tumors reflects strong ER transcriptional dependence. Elacestrant, an oral SERD, degrades ERα and suppresses early estrogen-regulated genes, and EMERALD shows greatest benefit in ESR1-mut/ER-dependent disease.</t>
+    </r>
+  </si>
+  <si>
+    <t>EMERALD: NCT03778931; PMID:35584336; PMID:28473534; PMID:36446866; PMID:27269946; MSigDB:HALLMARK_ESTROGEN_RESPONSE_EARLY</t>
   </si>
   <si>
     <r>
@@ -8791,8 +9382,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Some non-responders show transient TCR activation but rapidly develop counter-regulation (e.g., PD-1–independent anergy or Treg expansion), so an “up” TCR signature doesn’t always translate into tumor control.</t>
-    </r>
+      <t xml:space="preserve"> Extremely high estrogen-response with co-existing ESR1 LBD mutations plus PI3K/AKT hyperactivation or RB1 loss can drive partial ER independence, so even with ER degradation tumors may remain endocrine-refractory.</t>
+    </r>
+  </si>
+  <si>
+    <t>PMID:27986707; PMID:30205045; PMID:33375317; PMID:34298731; PMID:35584336</t>
   </si>
   <si>
     <r>
@@ -8806,8 +9400,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> In highly responsive tumors, rapid tumor clearance and contraction of effector T-cell pool can yield a lower TCR signature at bulk RNA level while the patient remains sensitive/clinical responder.</t>
-    </r>
+      <t xml:space="preserve"> Some “low-ER-score” luminal A tumors may still retain functional ER in a subset of clones; elacestrant can suppress residual ER signaling and prevent outgrowth of ESR1-mut subclones, giving modest but real benefit.</t>
+    </r>
+  </si>
+  <si>
+    <t>PMID:27269946; PMID:28473534; PMID:36446866; PMID:35584336</t>
   </si>
   <si>
     <r>
@@ -8821,8 +9418,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Failure of TCR re-invigoration (persistent low TCR signaling after treatment) due to intrinsic T-cell defects or dominant suppressive pathways predicts lack of response to PD-1 blockade.</t>
-    </r>
+      <t xml:space="preserve"> ER-low/basal-like or lineage-switched tumors show little estrogen-response at baseline and are largely ER-independent, so SERDs (including elacestrant) provide minimal benefit.</t>
+    </r>
+  </si>
+  <si>
+    <t>PMID:30205045; PMID:6788940 (review of ESR1/ER loss); PMID:33375317</t>
   </si>
   <si>
     <r>
@@ -8836,8 +9436,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> An inflamed IFN-γ gene signature (CXCL9/10, IDO1, HLA genes) in TNBC associates with TILs and better outcomes with PD-1/PD-L1 blockade, indicating pre-existing Th1/CD8⁺ immunity.</t>
-    </r>
+      <t xml:space="preserve"> In responders, elacestrant degrades ERα, reduces ER binding and profoundly downregulates early estrogen-response genes in PDX and clinical biopsies, consistent with on-target SERD activity and tumor regression.</t>
+    </r>
+  </si>
+  <si>
+    <t>PMID:28473534; PMID:36446866; PMID:33513026; PMID:35584336</t>
   </si>
   <si>
     <r>
@@ -8851,308 +9454,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Very strong IFN-γ signaling can select for JAK1/2 or B2M mutations, leading to eventual PD-1 resistance despite an initially high IFN signature.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Some TNBCs with modest IFN-γ signatures may still respond when cGAS–STING or neoantigen load is high and quickly induces an IFN-γ program after PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Lack of IFN-γ signaling (low STAT1-inducible genes) indicates poor antigen presentation and is a classic feature of primary PD-1 resistance.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Effective PD-1 blockade enhances CD8⁺ effector function, leading to a surge in IFN-γ–responsive transcripts and MHC I/PD-L1 induction, typical of responders.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In some non-responders, persistent IFN-γ may induce strong PD-L1, IDO1 and negative feedback while parallel JAK-STAT lesions in tumor cells blunt antiproliferative effects, yielding radiologic progression.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Once tumors regress, IFN-γ levels and corresponding signatures can normalize despite durable immune memory and ongoing sensitivity to retreatment.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Loss of IFN-γ signaling via JAK1/2 mutations during therapy leads to downregulation of IFN-γ–inducible genes and acquired resistance to PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Breast tumors with active cGAS–STING signaling (dsDNA sensing, type I IFN, chemokines) show higher immune infiltration and are more likely to respond to PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Chronic STING activation can drive immunosuppressive myeloid cells or exhaustion, so a high STING signature may occasionally coexist with primary resistance.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Low baseline cGAS–STING may still permit response if other innate pathways (e.g. viral STING agonists, RT-induced DNA damage) are activated around the time of PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cGAS–STING–deficient TNBCs are poorly inflamed and lack type I IFN priming, typically rendering PD-1 monotherapy ineffective.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (combo/indirect):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Radiotherapy or DNA-damaging chemo combined with dostarlimab can activate cGAS–STING, amplifying type I IFN and enhancing PD-1 response in breast cancer models.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Excessive STING activation may induce chronic inflammation with myeloid-dominant, suppressive microenvironments that counteract T-cell reinvigoration.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In deep responders, tumor eradication can reduce tumor DNA and STING engagement, lowering the signature despite maintained clinical sensitivity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tumors may downregulate cGAS or STING during immune editing, extinguishing type I IFN production and leading to secondary resistance to PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> High HLA-I/B2M/TAP expression and antigen-processing signatures in TNBC support efficient presentation of neoantigens to CD8⁺ T cells, favoring response to PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Some tumors with high MHC I still evade via other suppressive mechanisms (e.g. TGF-β, WNT, Tregs), leading to apparent resistance despite intact presentation.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Focally reduced MHC I may coexist with strong MHC II and cross-presentation by DCs, allowing PD-1 blockade to work if presentation is restored by IFN-γ.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Loss of B2M or defects in TAP/ERAP lead to poor MHC I antigen presentation, a classic cause of primary resistance to PD-1 inhibition.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Successful PD-1 blockade amplifies IFN-γ signaling, increasing MHC I/antigen-processing gene expression and epitope spreading, supporting durable control.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tumors may transiently increase MHC I yet still progress if downstream T cells are exhausted, deleted or excluded.</t>
-    </r>
+      <t xml:space="preserve"> ER program is suppressed but tumors escape via alternative survival circuits (e.g., PI3K/AKT, FGFR, cyclin E–CDK2), producing cytostatic but not cytotoxic effects and eventual progression despite a low estrogen-response signature.</t>
+    </r>
+  </si>
+  <si>
+    <t>PMID:30205045; PMID:33375317; PMID:34298731; PMID:34298731</t>
   </si>
   <si>
     <r>
@@ -9166,879 +9472,450 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> True reduction of antigen presentation in remaining tumor cells would undermine CD8-mediated control; any bulk “down” signature in a responder is more likely due to tumor clearance rather than a mechanism of sensitivity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Under immune pressure from PD-1 blockade, tumors may acquire B2M or HLA lesions, decreasing antigen presentation and causing acquired resistance.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> High stromal TGF-β signatures correlate with T-cell exclusion and poor response to PD-1/PD-L1 blockade, including in breast-cancer-like immune-excluded phenotypes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> A subset of TGF-β-high tumors may still respond if they also harbor very strong neoantigen load/TILs or are treated with combined TGF-β and PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Low TGF-β signaling reduces stromal exclusion, facilitating T-cell infiltration and better PD-1 responses in inflamed TNBC.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite low TGF-β implies other dominant immune escape mechanisms (e.g., WNT–β-catenin, IDO1), not TGF-β itself.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In responders, transient TGF-β upregulation may occur as negative feedback but generally does not drive sensitivity; durable benefit usually requires TGF-β to remain constrained.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Adaptive stromal TGF-β upregulation under PD-1 pressure can harden immune exclusion and drive resistance, motivating anti-TGF-β plus PD-1 combinations.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (combo):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Co-targeting TGF-β or stromal reprogramming with PD-1 blockade reduces TGF-β signaling, re-opens the stroma and enhances T-cell penetration, improving PD-1 efficacy.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Persistent resistance despite suppressed TGF-β suggests other escape nodes (e.g., JAK/STAT loss, MHC I loss, WNT activation).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> β-catenin activation drives DC and CD8⁺ T-cell exclusion and is linked to primary resistance to anti-PD-1 across solid tumors, likely including immune-excluded HER2-low/TNBC.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> WNT-high tumors may respond if concurrent factors (e.g., high mutational burden, strong chemotherapy-induced inflammation) override WNT-mediated exclusion.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Low WNT–β-catenin signaling permits DC recruitment and T-cell infiltration, favoring PD-1 blockade benefit in inflamed breast tumors.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite low WNT suggests other dominant suppressive pathways (TGF-β, IDO1, IL-10, tolerance).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically not possible:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> A rise in functional WNT–β-catenin signaling after PD-1 blockade would be expected to hinder, not promote, T-cell infiltration; any apparent association with sensitivity is artifactual.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tumors may upregulate WNT–β-catenin during PD-1 therapy as an adaptive escape, deepening T-cell exclusion and driving progression.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (combo):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Targeting WNT or its ligands (e.g. in trials) together with PD-1 blockade lowers β-catenin signaling, allows DC recruitment and enhances T-cell–mediated tumor clearance.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Continued resistance despite suppressed WNT suggests that other checkpoints or antigen-presentation defects dominate.</t>
-    </r>
-  </si>
-  <si>
-    <t>Spranger S et al. Nature 2015. https://pubmed.ncbi.nlm.nih.gov/25970248/; Muto S et al. Cancers (Basel) 2023. https://pmc.ncbi.nlm.nih.gov/articles/PMC9855612/</t>
-  </si>
-  <si>
-    <t>Spranger S et al. Nature 2015. https://pubmed.ncbi.nlm.nih.gov/25970248/; Wang B et al. Targeting Wnt/β-Catenin Signaling for Cancer Immunotherapy. Trends Pharmacol Sci 2018. https://www.sciencedirect.com/science/article/abs/pii/S0165614718300609</t>
-  </si>
-  <si>
-    <t>Muto S et al. Cancers (Basel) 2023. https://pmc.ncbi.nlm.nih.gov/articles/PMC9855612/; Mirlekar B et al. Tumor promoting roles of IL-10, TGF-β, IL-4, and IL-35. Semin Cancer Biol 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC8793114/</t>
-  </si>
-  <si>
-    <t>Spranger S et al. Nature 2015. https://pubmed.ncbi.nlm.nih.gov/25970248/; Wang B et al. Trends Pharmacol Sci 2018. https://www.sciencedirect.com/science/article/abs/pii/S0165614718300609</t>
-  </si>
-  <si>
-    <t>Spranger S et al. J Immunother Cancer 2015. https://jitc.bmj.com/content/3/1/43; Muto S et al. Cancers (Basel) 2023. https://pmc.ncbi.nlm.nih.gov/articles/PMC9855612/</t>
-  </si>
-  <si>
-    <t>Wang B et al. Trends Pharmacol Sci 2018. https://www.sciencedirect.com/article/abs/pii/S0165614718300609; Muto S et al. Cancers (Basel) 2023. https://pmc.ncbi.nlm.nih.gov/articles/PMC9855612/</t>
-  </si>
-  <si>
-    <t>Muto S et al. Cancers (Basel) 2023. https://pmc.ncbi.nlm.nih.gov/articles/PMC9855612/; Zaretsky JM et al. N Engl J Med 2016. https://www.nejm.org/doi/full/10.1056/NEJMoa1604958</t>
-  </si>
-  <si>
-    <t>The PI3K/Akt/mTOR Signaling Pathway in Triple-Negative Breast Cancer. Cancers (Basel) 2025. https://pmc.ncbi.nlm.nih.gov/articles/PMC12248877/; PD-L1 Expression in Triple-Negative Breast Cancer. Cancer Immunol Res 2014. https://aacrjournals.org/cancerimmunolres/article/2/4/361/467294/PD-L1-Expression-in-Triple-Negative-Breast; PD-1/PD-L1 interaction up-regulates MDR1/P-gp via PI3K/Akt and MAPK/Erk pathways. Oncotarget 2017. https://www.mdpi.com/1422-0067/26/14/6876</t>
-  </si>
-  <si>
-    <t>Garg P et al. Strategic advancements in targeting the PI3K/AKT/mTOR pathway in cancer immunotherapy. Biochim Biophys Acta Mol Cell Res 2025. https://www.sciencedirect.com/science/article/pii/S0006295225001121; André F et al. Alpelisib for PIK3CA-mutated, hormone receptor–positive advanced breast cancer. N Engl J Med 2019. https://www.nejm.org/doi/full/10.1056/NEJMoa1813904</t>
-  </si>
-  <si>
-    <t>Mittendorf EA et al. Cancer Immunol Res 2014. https://aacrjournals.org/cancerimmunolres/article/2/4/361/467294/PD-L1-Expression-in-Triple-Negative-Breast; Hassan A et al. Cancers (Basel) 2025. https://pmc.ncbi.nlm.nih.gov/articles/PMC12248877/</t>
-  </si>
-  <si>
-    <t>Özen Eroğlu G et al. Int J Mol Sci 2025. https://www.mdpi.com/1422-0067/26/14/6876; Zaretsky JM et al. N Engl J Med 2016. https://www.nejm.org/doi/full/10.1056/NEJMoa1604958</t>
-  </si>
-  <si>
-    <t>Okazaki T, Honjo T. PD-1 and PD-1 ligands: from discovery to clinical application. Int Immunol 2007. https://pubmed.ncbi.nlm.nih.gov/17606980/; Chakraborty A et al. Akt in immune cell function. Front Immunol 2022. https://www.frontiersin.org/articles/10.3389/fimmu.2022.951513/full</t>
-  </si>
-  <si>
-    <t>Mittendorf EA et al. Cancer Immunol Res 2014. https://aacrjournals.org/cancerimmunolres/article/2/4/361/467294/PD-L1-Expression-in-Triple-Negative-Breast; Li X et al. Development of a breast cancer invasion score to predict prognosis. Cell Death Discov 2025. https://www.nature.com/articles/s41420-025-02422-y</t>
-  </si>
-  <si>
-    <t>Garg P et al. Biochim Biophys Acta Mol Cell Res 2025. https://www.sciencedirect.com/science/article/pii/S0006295225001121; André F et al. N Engl J Med 2019. https://www.nejm.org/doi/full/10.1056/NEJMoa1813904</t>
-  </si>
-  <si>
-    <t>Zaretsky JM et al. N Engl J Med 2016. https://www.nejm.org/doi/full/10.1056/NEJMoa1604958; Shin DS et al. Cancer Discov 2017. https://pubmed.ncbi.nlm.nih.gov/27903500/</t>
-  </si>
-  <si>
-    <t>GOBP_TOLERANCE_INDUCTION_DEPENDENT_UPON_IMMUNE_RESPONSE</t>
-  </si>
-  <si>
-    <t>Schwartz RH. T cell anergy. Annu Rev Immunol 2003. https://pubmed.ncbi.nlm.nih.gov/12471050/; Zheng Y, Gajewski TF. Molecular regulation of T-cell anergy. EMBO Rep 2008. https://www.embopress.org/doi/10.1038/sj.embor.7401138; Qiu Y et al. FOXP3+ regulatory T cells and immune escape in solid tumours. Cancer Lett 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC9774953/</t>
-  </si>
-  <si>
-    <t>Schwartz RH. Annu Rev Immunol 2003. https://pubmed.ncbi.nlm.nih.gov/12471050/; Cortes J et al. Pembrolizumab plus chemotherapy in metastatic TNBC (KEYNOTE-355). N Engl J Med 2020. https://www.nejm.org/doi/full/10.1056/NEJMoa1910549</t>
-  </si>
-  <si>
-    <t>Plitas G, Rudensky AY. Regulatory T Cells in Cancer. Annu Rev Cancer Biol 2020. https://www.annualreviews.org/content/journals/10.1146/annurev-cancerbio-030419-033428; Itakura E et al. IL-10 expression by primary tumor cells correlates with tumor progression. Mod Pathol 2011. https://www.nature.com/articles/modpathol20115</t>
-  </si>
-  <si>
-    <t>Schwartz RH. Annu Rev Immunol 2003. https://pubmed.ncbi.nlm.nih.gov/12471050/; Shin DS et al. Cancer Discov 2017. https://pubmed.ncbi.nlm.nih.gov/27903500/</t>
-  </si>
-  <si>
-    <t>Zheng Y, Gajewski TF. EMBO Rep 2008. https://www.embopress.org/doi/10.1038/sj.embor.7401138; Plitas G, Rudensky AY. Annu Rev Cancer Biol 2020. https://www.annualreviews.org/content/journals/10.1146/annurev-cancerbio-030419-033428</t>
-  </si>
-  <si>
-    <t>Qiu Y et al. Cancer Lett 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC9774953/; Plitas G, Rudensky AY. Annu Rev Cancer Biol 2020. https://www.annualreviews.org/content/journals/10.1146/annurev-cancerbio-030419-033428</t>
-  </si>
-  <si>
-    <t>Cortes J et al. KEYNOTE-355. N Engl J Med 2020. https://www.nejm.org/doi/full/10.1056/NEJMoa1910549; Qiu Y et al. Cancer Lett 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC9774953/</t>
-  </si>
-  <si>
-    <t>Shin DS et al. Cancer Discov 2017. https://pubmed.ncbi.nlm.nih.gov/27903500/; Zaretsky JM et al. N Engl J Med 2016. https://www.nejm.org/doi/full/10.1056/NEJMoa1604958</t>
-  </si>
-  <si>
-    <t>GOBP_L_TRYPTOPHAN_CATABOLIC_PROCESS_TO_KYNURENINE</t>
-  </si>
-  <si>
-    <t>Tryptophan Catabolism as Immune Mechanism of Primary Resistance to Anti-PD-1. Front Immunol 2020. https://pmc.ncbi.nlm.nih.gov/articles/PMC7358280/; Liu M et al. Targeting the IDO1 pathway in cancer. J Hematol Oncol 2018. https://jhoonline.biomedcentral.com/articles/10.1186/s13045-018-0644-y; Opitz CA et al. The therapeutic potential of targeting tryptophan catabolism in cancer. Br J Cancer 2020. https://www.nature.com/articles/s41416-019-0664-6</t>
-  </si>
-  <si>
-    <t>Labadie BW et al. Reimagining IDO Pathway Inhibition in Cancer Immunotherapy. Clin Cancer Res 2019. https://aacrjournals.org/clincancerres/article/25/5/1462/82368/Reimagining-IDO-Pathway-Inhibition-in-Cancer; Botticelli A et al. Front Immunol 2020. https://pmc.ncbi.nlm.nih.gov/articles/PMC7358280/</t>
-  </si>
-  <si>
-    <t>Liu M et al. J Hematol Oncol 2018. https://jhoonline.biomedcentral.com/articles/10.1186/s13045-018-0644-y; Passarelli A et al. Targeting immunometabolism mediated by the IDO1 pathway. Front Immunol 2022. https://www.frontiersin.org/articles/10.3389/fimmu.2022.953115/full</t>
-  </si>
-  <si>
-    <t>Liu M et al. J Hematol Oncol 2018. https://jhoonline.biomedcentral.com/articles/10.1186/s13045-018-0644-y; Mor A et al. Kynurenines as a Novel Target for the Treatment of Lung Cancer. Pharmaceuticals (Basel) 2021. https://www.mdpi.com/1424-8247/14/7/606</t>
-  </si>
-  <si>
-    <t>Botticelli A et al. Front Immunol 2020. https://pmc.ncbi.nlm.nih.gov/articles/PMC7358280/; Labadie BW et al. Clin Cancer Res 2019. https://aacrjournals.org/clincancerres/article/25/5/1462/82368/Reimagining-IDO-Pathway-Inhibition-in-Cancer</t>
-  </si>
-  <si>
-    <t>Liu M et al. J Hematol Oncol 2018. https://jhoonline.biomedcentral.com/articles/10.1186/s13045-018-0644-y; Labadie BW et al. Clin Cancer Res 2019. https://aacrjournals.org/clincancerres/article/25/5/1462/82368/Reimagining-IDO-Pathway-Inhibition-in-Cancer</t>
-  </si>
-  <si>
-    <t>Mirlekar B et al. Semin Cancer Biol 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC8793114/; Shin DS et al. Cancer Discov 2017. https://pubmed.ncbi.nlm.nih.gov/27903500/</t>
-  </si>
-  <si>
-    <t>REACTOME_INTERLEUKIN_10_SIGNALING</t>
-  </si>
-  <si>
-    <t>Sato T et al. Interleukin 10 in the tumor microenvironment: a target for anticancer immunotherapy. Immunol Res 2011. https://pubmed.ncbi.nlm.nih.gov/22139852/; Mirlekar B et al. Tumor promoting roles of IL-10, TGF-β, IL-4, and IL-35. Semin Cancer Biol 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC8793114/; Itakura E et al. IL-10 expression by primary tumor cells correlates with tumor progression. Mod Pathol 2011. https://www.nature.com/articles/modpathol20115</t>
-  </si>
-  <si>
-    <t>Mocellin S et al. Interleukin-10 and the immune response against cancer. J Leukoc Biol 2005. https://jlb.onlinelibrary.wiley.com/doi/10.1189/jlb.0705358; Carlini V et al. The multifaceted nature of IL-10. Front Immunol 2023. https://www.frontiersin.org/articles/10.3389/fimmu.2023.1161067/full</t>
-  </si>
-  <si>
-    <t>Sato T et al. Immunol Res 2011. https://pubmed.ncbi.nlm.nih.gov/22139852/; Mirlekar B et al. Semin Cancer Biol 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC8793114/</t>
-  </si>
-  <si>
-    <t>Mirlekar B et al. Semin Cancer Biol 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC8793114/; Liu M et al. J Hematol Oncol 2018. https://jhoonline.biomedcentral.com/articles/10.1186/s13045-018-0644-y</t>
-  </si>
-  <si>
-    <t>Salkeni MA et al. Interleukin-10 in cancer immunotherapy: from bench to bedside. Semin Cancer Biol 2023. https://www.sciencedirect.com/science/article/abs/pii/S2405803323000869; Carlini V et al. Front Immunol 2023. https://www.frontiersin.org/articles/10.3389/fimmu.2023.1161067/full</t>
-  </si>
-  <si>
-    <t>Shin DS et al. Primary Resistance to PD-1 Blockade Mediated by JAK1/2 Mutations. Cancer Discov 2017. https://pubmed.ncbi.nlm.nih.gov/27903500/; Zaretsky JM et al. Mutations associated with acquired resistance to PD-1 blockade. N Engl J Med 2016. https://www.nejm.org/doi/full/10.1056/NEJMoa1604958</t>
-  </si>
-  <si>
-    <t>Zielińska MK et al. Mechanisms of Resistance to Anti-PD-1 Immunotherapy. Biomolecules 2025. https://www.mdpi.com/2218-273X/15/2/269; Perner F et al. Malignant JAK-signaling: at the interface of inflammation and neoplasia. Leukemia 2025. https://www.nature.com/articles/s41375-025-02569-8</t>
-  </si>
-  <si>
-    <t>Zaretsky JM et al. N Engl J Med 2016. https://www.nejm.org/doi/full/10.1056/NEJMoa1604958; Zielińska MK et al. Biomolecules 2025. https://www.mdpi.com/2218-273X/15/2/269</t>
-  </si>
-  <si>
-    <t>Zielińska MK et al. Biomolecules 2025. https://www.mdpi.com/2218-273X/15/2/269; Mirlekar B et al. Semin Cancer Biol 2022. https://pmc.ncbi.nlm.nih.gov/articles/PMC8793114/</t>
-  </si>
-  <si>
-    <t>Shin DS et al. Cancer Discov 2017. https://pubmed.ncbi.nlm.nih.gov/27903500/; Zaretsky JM et al. N Engl J Med 2016. https://www.nejm.org/doi/full/10.1056/NEJMoa1604958; DOI:10.1158/2159-8290.CD-16-1223</t>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Oncogenic PI3K/AKT/mTOR activation in breast cancer (e.g., PIK3CA mutations) promotes PD-L1 expression and immunosuppressive metabolism, often correlating with reduced ICI benefit.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PI3K-hyperactivated but highly immunogenic TNBC may still respond, particularly when combined with PI3K inhibitors plus PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Lower PI3K/AKT activity may correspond to less PD-L1 upregulation and a more permissive immune microenvironment, aiding PD-1 response.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite low PAM activity implies alternate escape via TGF-β, WNT or antigen-presentation loss.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PD-1 blockade can enhance PI3K signaling in T cells (via CD28), supporting effector function, but tumor-cell PAM upregulation generally opposes sensitivity; net “up” with benefit is context-dependent.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Under PD-1 pressure, tumor clones with higher PI3K/AKT/mTOR activity (e.g., PTEN loss) may be selected, increasing PD-L1 and survival and mediating resistance.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (combo):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Adding PI3K/mTOR inhibitors to dostarlimab reduces tumor-cell PAM signaling and PD-L1 expression, improving T-cell function and checkpoint efficacy in PAM-driven TNBC.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Persisting resistance despite PAM suppression suggests that survival now depends on alternative escapes (e.g., JAK/STAT loss, MHC I loss, TGF-β).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> High signatures of T-cell anergy/Treg-mediated tolerance (GO:0002461; anergy genes, FOXP3) in breast tumors indicate an immune-tolerant state where PD-1 blockade alone is often insufficient.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In some settings, partial tolerance signatures may coexist with a large effector pool that can still be reactivated by PD-1 blockade plus chemotherapy or radiation.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Low tolerance/anergy gene expression with active effector signatures in TNBC predicts a microenvironment where PD-1 blockade can easily amplify pre-existing responses.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite low tolerance suggests absence of T cells (true desert) or other tumor-intrinsic defects (e.g., JAK/MHC I).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically not possible:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Increased tolerance induction after PD-1 blockade would be expected to counteract, not support, sensitivity; any correlation with benefit is likely confounding.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Non-responding breast tumors may adapt by expanding FOXP3⁺ Tregs or inducing anergy pathways, increasing tolerance signatures under PD-1 blockade and causing resistance.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In responders, PD-1 blockade plus chemo can reduce Treg/ tolerance programs, lowering tolerance signatures and enabling robust effector responses.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite reduced tolerance suggests that other blocks (e.g., loss of IFN-γ/JAK-STAT, antigen loss) dominate.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> High IDO1/TDO expression and KYN/Trp ratio in TNBC promote T-cell suppression and Treg expansion, conferring primary resistance to anti-PD-1 monotherapy.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> IDO1-high tumors may respond if IDO1 is co-inhibited or if strong neoantigen load and chemo override the metabolic brake.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Low IDO1/TDO activity maintains tryptophan and limits KYN, preserving effector CD8⁺/NK function and favoring PD-1 response.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite low KYN metabolism implies escape via other checkpoints or antigen-presentation/JAK defects.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically not possible:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> An increase in IDO1/TDO-driven KYN after PD-1 blockade would be expected to dampen, not enhance, anti-tumor immunity; any apparent link to sensitivity is artifactual.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Non-responders often show compensatory IDO1 induction in tumor/myeloid cells under PD-1 therapy, increasing KYN and reinforcing immune suppression.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (combo):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> IDO1 inhibition or loss of IDO1-high clones during effective PD-1 therapy decreases KYN production, enabling stronger T-cell responses.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance with low IDO1/KYN indicates that other suppressive axes (e.g., TGF-β, WNT, JAK/MHC defects) now dominate.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (tumor-derived IL-10):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> High IL-10 in the TNBC microenvironment suppresses antigen-presenting cells and CD8⁺/NK function, favoring immune escape and poorer ICI responses.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare (context-dependent):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In some contexts, IL-10/IL-10R signaling can maintain a PD-1^int TCF1⁺ progenitor CD8⁺ pool that supports long-term responses to PD-1 blockade.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate (for suppressive IL-10):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Low IL-10 in breast tumors reduces immunosuppressive skewing of myeloid cells, allowing more effective PD-1-mediated T-cell activation.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite low IL-10 suggests other suppression (Tregs, TGF-β, IDO1) rather than IL-10.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare/ambiguous:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Therapeutic IL-10 agonism can, in some systems, boost CD8⁺ expansion and synergize with PD-1, but this is experimental and not a typical driver of sensitivity in breast cancer.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Chronic IL-10 induction by tumor or B cells after PD-1 blockade can dampen inflammation and is associated with reduced T-cell cytotoxicity and ICI resistance.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically accurate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In responders, effective therapy and modulation of the microenvironment may lower suppressive IL-10 levels, allowing sustained effector T-cell activity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mechanistically rare:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resistance despite reduced IL-10 points to other dominant resistance mechanisms (e.g., JAK/STAT mutations, antigen loss, WNT/TGF-β).</t>
-    </r>
+      <t xml:space="preserve"> Sustained increase in early ER-regulated transcription despite continuous SERD dosing implies lack of ER engagement or assay artifact; such a pattern would contradict true pharmacodynamic response and would not be associated with sensitivity.</t>
+    </r>
+  </si>
+  <si>
+    <t>Conceptual PD argument; EMERALD PK/PD: PMID:32661909; label: ORSERDU FDA label 2023</t>
+  </si>
+  <si>
+    <r>
+      <t>Mechanistically accurate (signature-level):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Persistent or rebound estrogen-response (e.g., due to ESR1 Y537S/D538G, ER splice variants or drug-tolerant ER pools) indicates pharmacodynamic failure; these tumors show primary or acquired resistance to elacestrant.</t>
+    </r>
+  </si>
+  <si>
+    <t>PMID:27986707; PMID:36446866; PMID:27269946; PMID:30205045</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Elacestrant </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KEGG_MEDICUS_REFERENCE_NUCLEAR_INITIATED_ESTROGEN_SIGNALING_PATHWAY </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Before </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Up </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sensitive </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Strong nuclear ER signaling (ligand-dependent ESR1 transcriptional program) typifies classical endocrine-sensitive ER+ disease; elacestrant effectively disrupts this nuclear ER axis and improves PFS vs SOC ET in such patients. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Resistant </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Highly activated nuclear ER signaling driven by activating ESR1 mutations plus co-amplified co-activators (e.g., FOXA1, NCOR loss) can reduce SERD potency, conferring relative SERD resistance even with a high nuclear ER signature. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:27986707; PMID:36446866; PMID:30205045; PMID:6788940 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Down </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Modestly low nuclear ER signaling but persistent ER dependence (e.g., low E2 environment, partial ER silencing) may still be exploitable by SERD therapy, especially in combination with CDK4/6 inhibition. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:31852484; PMID:33513026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: When nuclear ER signaling is already low from ER loss, promoter methylation or lineage switch (basal-like/NE-like), elacestrant has little target and is unlikely to provide benefit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:30205045; PMID:6788940 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> After </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: PD studies with FES-PET and biopsies show marked reduction of nuclear ER availability and downstream transcription after elacestrant, aligning with tumor responses and clinical benefit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:36446866; PMID:32661909; NCT03778931 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Nuclear ER signaling is suppressed but alternative transcriptional drivers (AP-1, NF-κB, growth-factor–driven ER-independent programs) maintain proliferation, yielding clinical resistance despite apparently adequate ER degradation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:30205045; PMID:33375317; PMID:34298731 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: A true increase in nuclear ER signaling in the presence of an active SERD would mean ER degradation is not occurring; sensitivity under these conditions is not biologically consistent. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate (signature-level): Rebound nuclear ER signaling (e.g., via emergent ESR1 mutations or clonal selection) under elacestrant pressure is a hallmark of acquired SERD resistance and predicts poor outcomes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:27986707; PMID:36446866; PMID:27269946; PMID:30205045 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WP_ESTROGEN_SIGNALING </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: High WP_ESTROGEN_SIGNALING (integrated genomic + non-genomic ER plus growth-factor crosstalk) in HR+ tumors still largely dependent on ER makes them ideal candidates for elacestrant, often with additional benefit from CDK4/6 or PI3K inhibition. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Strong ER/non-genomic signaling plus HER2/EGFR activation and PI3K/AKT hyperactivity can drive partial ER independence; in such “hyper-wired” tumors, ER degradation alone gives limited control and combination targeted therapy is needed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:33375317; PMID:34298731; PMID:30205045; PMID:41523-023-00533-2 (HER2/ER crosstalk) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Some luminal tumors show modest estrogen-signaling scores due to prior AI exposure but remain partially ER-addicted; elacestrant can resuppress residual ER activity and delay outgrowth of resistant clones. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:31852484; PMID:27269946 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: When both genomic and non-genomic ER signaling are low (e.g., ER-negative/basal or heavily dedifferentiated HR+ tumors), elacestrant lacks a meaningful target and response is unlikely. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Effective ER degradation reduces both nuclear signaling and membrane-proximal ER crosstalk with RTKs (e.g., HER2, IGF1R), lowering WP_ESTROGEN_SIGNALING scores and correlating with tumor control. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:36446866; PMID:28473534; PMID:33375317; PMID:35584336 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: WP_ESTROGEN_SIGNALING falls, but tumors rapidly rewire to HER2, FGFR, or GPCR-driven growth independent of ER, producing resistant disease despite suppression of the canonical estrogen pathway. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:30205045; PMID:33375317; PMID:34298731; PMID:41523-023-00533-2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: True biological upregulation of net estrogen signaling in the presence of pharmacodynamically active elacestrant would mean failure of ER occupancy/degradation; such a profile is incompatible with genuine sensitivity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate (signature-level): Increased or persistent estrogen-signaling scores after treatment reflect ineffective ER targeting or emergence of ER variants, defining primary or acquired resistance. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HALLMARK_ESTROGEN_RESPONSE_LATE </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: High late estrogen-response (cell-cycle/proliferation-linked ER program) in luminal B–like tumors indicates ER-driven proliferation; SERD-mediated shutdown of this late program underlies elacestrant activity, especially with CDK4/6i. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Very high late estrogen-response plus RB1 loss or CCNE1 amplification can render tumors E2F-driven and only partially ER-dependent, so SERD monotherapy may underperform without added CDK or PI3K pathway blockade. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:30205045; PMID:34298731; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate (indolent luminal): Low late ER-response in luminal A tumors reflects slower cycling but preserved ER dependence; elacestrant can durably maintain suppression with relatively modest PD changes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:27269946; PMID:35584336; PMID:28473534 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Late ER program is low because the tumor has already shifted to ER-independent cell-cycle drivers (e.g., MAPK, HER2, PI3K); these tumors often show endocrine resistance and limited benefit from elacestrant. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:30205045; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: In responding lesions, elacestrant reduces late estrogen-response and G1/S transition genes, consistent with arrest and regression, especially where ER-E2F coupling is intact. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:36446866; PMID:28473534; PMID:33513026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Late ER-response falls but parallel pathways (e.g., CDK2/cyclin E or MYC) maintain proliferation, yielding clinical resistance despite low hallmark scores. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: Increased late ER-responsive transcription under SERD exposure would indicate lack of target engagement; such a pattern would be incompatible with true sensitivity to elacestrant. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate (signature-level): Rebound in late ER-response and cycling genes after an initial drop indicates acquired resistance with restoration of ER signaling or E2F uncoupling from ER control. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:27986707; PMID:30205045; PMID:36446866 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HALLMARK_E2F_TARGETS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Moderately high E2F targets in ER+ tumors with intact RB can still be ER-driven; SERD plus CDK4/6 blockade is particularly effective in this context, but elacestrant monotherapy alone may only partially control proliferation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Marked E2F upregulation driven by RB1 loss, CCNE1 amplification or CDK2 activation is a key endocrine-resistance mechanism; these tumors are poorly controlled by ER-directed agents including elacestrant. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:30205045; PMID:36446866; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Low E2F-target expression reflects indolent luminal A biology with intact cell-cycle checkpoints, where ER dependence is high and SERDs remain highly effective. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:27269946; PMID:35584336 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Rare ER+ tumors with low cycling but strong survival signaling (e.g., PI3K, BCL2) may show endocrine resistance despite quiescent E2F signatures. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:33375317; PMID:34298731 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: In sensitive tumors, elacestrant reduces E2F-target transcription as ER-driven cyclin D/CDK4/6 signaling is diminished, translating into cell-cycle arrest. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:36446866; PMID:31852484 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Some cells enter a reversible quiescent state with low E2F but survive via autophagy or alternative survival pathways, leading to eventual regrowth despite suppressed E2F targets. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: A durable increase in E2F-target expression after ER degradation is incompatible with true antiproliferative response; it would indicate that the dominant driver is no longer ER and that cells will not be genuinely sensitive. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Conceptual cell-cycle logic; ER+ resistance genomics: PMID:30205045 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Adaptive upregulation of E2F targets (via RB loss or cyclin E upregulation) after initial SERD exposure is a recognized escape route and marks acquired resistance. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HALLMARK_G2M_CHECKPOINT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Highly proliferative ER+ luminal B tumors with intact checkpoints may respond to ER removal, but maximal benefit often requires combination (CDK4/6 or chemo); elacestrant alone may yield partial sensitivity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Marked G2/M upregulation often reflects aggressive, genomically unstable disease with multiple non-ER drivers (e.g., TNBC-like or HER2-amp), where SERD monotherapy has limited impact. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: ER+ tumors with low G2/M activity are less proliferative but still hormone-driven, so SERDs can maintain durable control without needing to counteract strong G2/M signaling. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Some slow-cycling but endocrine-resistant clones (e.g., with ESR1 mutation plus PI3K activation) show low G2/M signatures yet do not respond to ER-directed therapy. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:27269946; PMID:30205045; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: In responders, ER downregulation leads to reduced S-phase entry and G2/M checkpoint activation, consistent with decreased mitoses and tumor shrinkage. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:36446866 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Even with decreased G2/M signaling, some cells may persist in a dormant state with later reactivation, producing radiologic stability followed by late progression. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: Sustained increase in G2/M signature post-SERD, without other interventions, represents ongoing proliferation and is inconsistent with a truly sensitive phenotype. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> General cell-cycle logic; endocrine resistance overviews: PMID:33375317; PMID:34298731 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: G2/M signature maintenance or increase after elacestrant indicates ER-independent proliferative control (e.g., via HER2 or PI3K/AKT), and associates with poor response. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HALLMARK_MTORC1_SIGNALING </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Some ER+ tumors with moderate mTORC1 activation remain ER-addicted; they can benefit from elacestrant but are ideal candidates for combination with mTOR or PI3K/AKT inhibitors. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Strong mTORC1 activation (via PIK3CA mutation, PTEN loss, RTK activation) is a classic endocrine-resistance pathway, blunting efficacy of ER-targeted agents including SERDs when used alone. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:33375317; PMID:34298731; PMID:34298731; PMID:38561964 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Low mTORC1 implies limited growth-factor or nutrient-sensing bypass; ER remains the dominant driver and SERD monotherapy can be highly effective. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:33375317; PMID:35584336 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: A subset of endocrine-resistant tumors may evade ER targeting via MAPK/FGFR or epigenetic rewiring without overt mTORC1 activation, so low mTORC1 does not guarantee sensitivity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate (indirect): By shutting down ER-driven RTK and growth-factor signaling, elacestrant can secondarily decrease mTORC1 activity in sensitive tumors, aligning with improved outcomes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:36446866; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: mTORC1 falls but cells rely on alternative survival circuits (e.g., autophagy, MAPK), leading to disease stabilization rather than objective responses. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:34298731; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: Persistent mTORC1 upregulation after SERD treatment promotes protein synthesis and survival, incompatible with genuine drug sensitivity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logic from PI3K/mTOR biology; PMID:33375317; PMID:34298731 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Adaptive mTORC1 upregulation (e.g., via insulin/IGF1R signaling) after ER blockade is a known escape route underlying poor response to endocrine therapy alone. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:33375317; PMID:34298731; PMID:38561964 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HALLMARK_PI3K_AKT_MTOR_SIGNALING </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Moderately elevated PI3K/AKT/mTOR signaling can coexist with ER dependence; such tumors often require ER plus PI3K/AKT pathway inhibition for optimal control, so elacestrant alone yields partial but not maximal sensitivity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Strong PI3K/AKT activation (PIK3CA mutation, PTEN loss) is a central endocrine-resistance driver; elacestrant monotherapy is commonly insufficient without co-targeting PI3K/AKT. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Low PI3K/AKT/mTOR signaling indicates minimal growth-factor bypass; ER remains dominant, and SERDs achieve robust and durable disease control. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Rare tumors may be driven by alternative pathways (e.g., MAPK, FGFR) with low PI3K signal yet show endocrine resistance. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate (indirect): In responding tumors, ER shutdown leads to reduced RTK signaling and downstream PI3K/AKT, aligning with improved PFS and deeper responses. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: PI3K/AKT signature decreases modestly, but compensatory survival mechanisms (altered metabolism, autophagy) maintain viability, so clinical benefit is limited. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: Sustained upregulation of PI3K/AKT/mTOR signaling promotes survival and is incompatible with genuine endocrine/SERD sensitivity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Conceptual; PI3K resistance: PMID:33375317; PMID:34298731; PMID:38561964 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Adaptive activation of PI3K/AKT after ER blockade is a classic resistance loop that undermines elacestrant monotherapy. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:33375317; PMID:34298731; PMID:34298731 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KEGG_ERBB_SIGNALING_PATHWAY </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: In HR+/HER2-low tumors with modest ERBB signaling, ER remains a key driver; elacestrant can be beneficial, especially when combined with HER2-directed agents in HR+/HER2+ disease. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Strong HER2/ERBB activation (HER2+ or HER3-driven) promotes ligand-independent ER phosphorylation and endocrine resistance, making SERD monotherapy inadequate. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:37258523; PMID:30205045; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: In HER2-negative, ER-driven tumors with low ERBB signaling, elacestrant effectively targets the dominant ER axis. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:35584336; PMID:37258523 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Resistance may arise via non-ERBB drivers (PI3K, FGFR, MAPK) despite low ERBB signature, limiting elacestrant benefit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate (indirect): ER degradation can reduce ER-dependent HER2/HER3 transcription and feedback RTK signaling, leading to decreased ERBB pathway activity in sensitive HR+/HER2-low tumors. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:36446866; PMID:37258523 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: ERBB signature decreases but parallel RTKs (e.g., FGFR, IGF1R) maintain downstream PI3K/AKT, producing only modest benefit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:33375317; PMID:34298731; PMID:37258523 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: True upregulation of HER2/ERBB signaling while maintaining durable sensitivity to ER degradation is biologically inconsistent; such tumors typically escape endocrine control. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistic logic; HER2/ER crosstalk review: PMID:37258523 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Adaptive ERBB upregulation after ER blockade (HER2/HER3 “bounce-back”) is a recognized escape route driving resistance to endocrine therapy and SERDs. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HALLMARK_APOPTOSIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Tumors with a primed apoptotic machinery (e.g., intact p53, pro-apoptotic BH3 expression) can undergo apoptosis once ER-dependent survival signaling is removed by elacestrant. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Despite a pro-apoptotic gene signature, high anti-apoptotic BCL2/BCL-XL or strong PI3K signaling can block cell death, yielding relative resistance to ER-directed therapy. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Some ER+ tumors with low basal apoptosis can still be pushed into apoptosis when ER is removed, especially in combination with CDK4/6 or BCL2 inhibitors. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:31852484 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Apoptosis-low, survival-high signatures (high BCL2, MCL1, XIAP) associate with poor endocrine response; elacestrant alone may mainly cause cytostasis. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically not possible: A decrease in apoptotic signaling after ER deprivation would not plausibly underlie true sensitivity; durable benefit requires at least maintained, if not increased, apoptotic priming. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Class logic; SERD PD: PMID:35923930; PMID:28473534 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: Tumors that upregulate anti-apoptotic programs (BCL2/BCL-XL, MCL1) or downregulate pro-apoptotic genes after SERD exposure evade cell death and present as resistant. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically accurate: In responders, elacestrant reduces ER-mediated survival signaling and can increase expression or activation of pro-apoptotic effectors, leading to tumor cell apoptosis in PDX and clinical biopsies. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:28473534; PMID:36446866; PMID:33513026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mechanistically rare: Transient apoptosis upregulation may occur in a subset of cells, but selection of resistant clones or strong compensatory survival signaling leads to overall clinical resistance. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:35584336; PMID:33513026; PMID:28473534 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:35923930; PMID:30205045 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PMID:35584336; PMID:36446866; PMID:33375317 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:35584336; PMID:28473534; PMID:36446866; PMID:31852484 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:35923930; PMID:32661909 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:31852484; PMID:35584336; PMID:30205045 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:31852484; PMID:35584336 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:33375317; PMID:34298731; PMID:35584336 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:33375317; PMID:34298731; PMID:34298731; PMID:38561964 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:37258523; PMID:35584336 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID:28473534; PMID:36446866 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10067,6 +9944,12 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -10089,7 +9972,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -10110,6 +9993,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10445,10 +10329,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F09584A-6957-4626-A38A-643C86F416A6}">
-  <dimension ref="A1:H665"/>
+  <dimension ref="A1:H745"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="51.6328125" customWidth="1"/>
     <col min="3" max="3" width="16.7265625" customWidth="1"/>
     <col min="4" max="4" width="12.26953125" customWidth="1"/>
     <col min="5" max="5" width="13.6328125" customWidth="1"/>
@@ -24656,7 +24540,7 @@
         <v>1211</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C618" s="3" t="s">
         <v>5</v>
@@ -24668,10 +24552,10 @@
         <v>7</v>
       </c>
       <c r="F618" s="5" t="s">
-        <v>1253</v>
+        <v>1244</v>
       </c>
       <c r="G618" s="4" t="s">
-        <v>1222</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="619" spans="1:7">
@@ -24679,7 +24563,7 @@
         <v>1211</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C619" s="3" t="s">
         <v>5</v>
@@ -24691,10 +24575,10 @@
         <v>25</v>
       </c>
       <c r="F619" s="5" t="s">
-        <v>1254</v>
+        <v>1245</v>
       </c>
       <c r="G619" s="4" t="s">
-        <v>1223</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="620" spans="1:7">
@@ -24702,7 +24586,7 @@
         <v>1211</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C620" s="3" t="s">
         <v>5</v>
@@ -24714,10 +24598,10 @@
         <v>7</v>
       </c>
       <c r="F620" s="5" t="s">
-        <v>1255</v>
+        <v>1246</v>
       </c>
       <c r="G620" s="4" t="s">
-        <v>1224</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="621" spans="1:7">
@@ -24725,7 +24609,7 @@
         <v>1211</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C621" s="3" t="s">
         <v>5</v>
@@ -24737,10 +24621,10 @@
         <v>25</v>
       </c>
       <c r="F621" s="5" t="s">
-        <v>1256</v>
+        <v>1247</v>
       </c>
       <c r="G621" s="4" t="s">
-        <v>1225</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -24748,7 +24632,7 @@
         <v>1211</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C622" s="3" t="s">
         <v>9</v>
@@ -24760,10 +24644,10 @@
         <v>7</v>
       </c>
       <c r="F622" s="5" t="s">
-        <v>1257</v>
+        <v>1248</v>
       </c>
       <c r="G622" s="4" t="s">
-        <v>1226</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="623" spans="1:7">
@@ -24771,7 +24655,7 @@
         <v>1211</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C623" s="3" t="s">
         <v>9</v>
@@ -24783,10 +24667,10 @@
         <v>25</v>
       </c>
       <c r="F623" s="5" t="s">
-        <v>1258</v>
+        <v>1249</v>
       </c>
       <c r="G623" s="4" t="s">
-        <v>1223</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -24794,7 +24678,7 @@
         <v>1211</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C624" s="3" t="s">
         <v>9</v>
@@ -24806,10 +24690,10 @@
         <v>7</v>
       </c>
       <c r="F624" s="5" t="s">
-        <v>1259</v>
+        <v>1250</v>
       </c>
       <c r="G624" s="4" t="s">
-        <v>1227</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -24817,7 +24701,7 @@
         <v>1211</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C625" s="3" t="s">
         <v>9</v>
@@ -24829,10 +24713,10 @@
         <v>25</v>
       </c>
       <c r="F625" s="5" t="s">
-        <v>1260</v>
+        <v>1251</v>
       </c>
       <c r="G625" s="4" t="s">
-        <v>1228</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="626" spans="1:7">
@@ -24840,7 +24724,7 @@
         <v>1211</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C626" s="3" t="s">
         <v>5</v>
@@ -24852,10 +24736,10 @@
         <v>7</v>
       </c>
       <c r="F626" s="5" t="s">
-        <v>1261</v>
+        <v>1252</v>
       </c>
       <c r="G626" t="s">
-        <v>1230</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -24863,7 +24747,7 @@
         <v>1211</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C627" s="3" t="s">
         <v>5</v>
@@ -24875,10 +24759,10 @@
         <v>25</v>
       </c>
       <c r="F627" s="5" t="s">
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="G627" t="s">
-        <v>1231</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -24886,7 +24770,7 @@
         <v>1211</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C628" s="3" t="s">
         <v>5</v>
@@ -24898,10 +24782,10 @@
         <v>7</v>
       </c>
       <c r="F628" s="5" t="s">
-        <v>1263</v>
+        <v>1254</v>
       </c>
       <c r="G628" t="s">
-        <v>1232</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="629" spans="1:7">
@@ -24909,7 +24793,7 @@
         <v>1211</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C629" s="3" t="s">
         <v>5</v>
@@ -24921,10 +24805,10 @@
         <v>25</v>
       </c>
       <c r="F629" s="5" t="s">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="G629" t="s">
-        <v>1233</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -24932,7 +24816,7 @@
         <v>1211</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C630" s="3" t="s">
         <v>9</v>
@@ -24944,10 +24828,10 @@
         <v>7</v>
       </c>
       <c r="F630" s="5" t="s">
-        <v>1265</v>
+        <v>1256</v>
       </c>
       <c r="G630" t="s">
-        <v>1234</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -24955,7 +24839,7 @@
         <v>1211</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C631" s="3" t="s">
         <v>9</v>
@@ -24967,10 +24851,10 @@
         <v>25</v>
       </c>
       <c r="F631" s="5" t="s">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="G631" t="s">
-        <v>1235</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="632" spans="1:7">
@@ -24978,7 +24862,7 @@
         <v>1211</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C632" s="3" t="s">
         <v>9</v>
@@ -24990,10 +24874,10 @@
         <v>7</v>
       </c>
       <c r="F632" s="5" t="s">
-        <v>1267</v>
+        <v>1258</v>
       </c>
       <c r="G632" t="s">
-        <v>1236</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -25001,7 +24885,7 @@
         <v>1211</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C633" s="3" t="s">
         <v>9</v>
@@ -25013,10 +24897,10 @@
         <v>25</v>
       </c>
       <c r="F633" s="5" t="s">
-        <v>1268</v>
+        <v>1259</v>
       </c>
       <c r="G633" t="s">
-        <v>1234</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -25036,10 +24920,10 @@
         <v>7</v>
       </c>
       <c r="F634" s="5" t="s">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="G634" t="s">
-        <v>1237</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -25059,10 +24943,10 @@
         <v>25</v>
       </c>
       <c r="F635" s="5" t="s">
-        <v>1270</v>
+        <v>1261</v>
       </c>
       <c r="G635" t="s">
-        <v>1223</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="636" spans="1:7">
@@ -25082,10 +24966,10 @@
         <v>7</v>
       </c>
       <c r="F636" s="5" t="s">
-        <v>1271</v>
+        <v>1262</v>
       </c>
       <c r="G636" t="s">
-        <v>1237</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -25105,10 +24989,10 @@
         <v>25</v>
       </c>
       <c r="F637" s="5" t="s">
-        <v>1272</v>
+        <v>1263</v>
       </c>
       <c r="G637" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -25128,10 +25012,10 @@
         <v>7</v>
       </c>
       <c r="F638" s="5" t="s">
-        <v>1273</v>
+        <v>1264</v>
       </c>
       <c r="G638" t="s">
-        <v>1237</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -25151,10 +25035,10 @@
         <v>25</v>
       </c>
       <c r="F639" s="5" t="s">
-        <v>1274</v>
+        <v>1265</v>
       </c>
       <c r="G639" t="s">
-        <v>1223</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="640" spans="1:7">
@@ -25174,10 +25058,10 @@
         <v>7</v>
       </c>
       <c r="F640" s="5" t="s">
-        <v>1275</v>
+        <v>1266</v>
       </c>
       <c r="G640" t="s">
-        <v>1239</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="641" spans="1:7">
@@ -25197,10 +25081,10 @@
         <v>25</v>
       </c>
       <c r="F641" s="5" t="s">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="G641" t="s">
-        <v>1240</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="642" spans="1:7">
@@ -25208,7 +25092,7 @@
         <v>1211</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C642" s="3" t="s">
         <v>5</v>
@@ -25220,10 +25104,10 @@
         <v>7</v>
       </c>
       <c r="F642" s="5" t="s">
-        <v>1277</v>
+        <v>1268</v>
       </c>
       <c r="G642" t="s">
-        <v>1242</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="643" spans="1:7">
@@ -25231,7 +25115,7 @@
         <v>1211</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C643" s="3" t="s">
         <v>5</v>
@@ -25243,10 +25127,10 @@
         <v>25</v>
       </c>
       <c r="F643" s="5" t="s">
-        <v>1278</v>
+        <v>1269</v>
       </c>
       <c r="G643" t="s">
-        <v>1243</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="644" spans="1:7">
@@ -25254,7 +25138,7 @@
         <v>1211</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C644" s="3" t="s">
         <v>5</v>
@@ -25266,10 +25150,10 @@
         <v>7</v>
       </c>
       <c r="F644" s="5" t="s">
-        <v>1279</v>
+        <v>1270</v>
       </c>
       <c r="G644" t="s">
-        <v>1244</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="645" spans="1:7">
@@ -25277,7 +25161,7 @@
         <v>1211</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C645" s="3" t="s">
         <v>5</v>
@@ -25289,10 +25173,10 @@
         <v>25</v>
       </c>
       <c r="F645" s="5" t="s">
-        <v>1280</v>
+        <v>1271</v>
       </c>
       <c r="G645" t="s">
-        <v>1242</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="646" spans="1:7">
@@ -25300,7 +25184,7 @@
         <v>1211</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C646" s="3" t="s">
         <v>9</v>
@@ -25312,10 +25196,10 @@
         <v>7</v>
       </c>
       <c r="F646" s="5" t="s">
-        <v>1281</v>
+        <v>1272</v>
       </c>
       <c r="G646" t="s">
-        <v>1242</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="647" spans="1:7">
@@ -25323,7 +25207,7 @@
         <v>1211</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C647" s="3" t="s">
         <v>9</v>
@@ -25335,10 +25219,10 @@
         <v>25</v>
       </c>
       <c r="F647" s="5" t="s">
-        <v>1282</v>
+        <v>1273</v>
       </c>
       <c r="G647" t="s">
-        <v>1243</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="648" spans="1:7">
@@ -25346,7 +25230,7 @@
         <v>1211</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C648" s="3" t="s">
         <v>9</v>
@@ -25358,10 +25242,10 @@
         <v>7</v>
       </c>
       <c r="F648" s="5" t="s">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="G648" t="s">
-        <v>1244</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="649" spans="1:7">
@@ -25369,7 +25253,7 @@
         <v>1211</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C649" s="3" t="s">
         <v>9</v>
@@ -25381,10 +25265,10 @@
         <v>25</v>
       </c>
       <c r="F649" s="5" t="s">
-        <v>1284</v>
+        <v>1275</v>
       </c>
       <c r="G649" t="s">
-        <v>1244</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="650" spans="1:7">
@@ -25392,7 +25276,7 @@
         <v>1211</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C650" s="3" t="s">
         <v>5</v>
@@ -25404,10 +25288,10 @@
         <v>7</v>
       </c>
       <c r="F650" s="5" t="s">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="G650" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="651" spans="1:7">
@@ -25415,7 +25299,7 @@
         <v>1211</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C651" s="3" t="s">
         <v>5</v>
@@ -25427,10 +25311,10 @@
         <v>25</v>
       </c>
       <c r="F651" s="5" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="G651" t="s">
-        <v>1247</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="652" spans="1:7">
@@ -25438,7 +25322,7 @@
         <v>1211</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C652" s="3" t="s">
         <v>5</v>
@@ -25450,10 +25334,10 @@
         <v>7</v>
       </c>
       <c r="F652" s="5" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="G652" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="653" spans="1:7">
@@ -25461,7 +25345,7 @@
         <v>1211</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C653" s="3" t="s">
         <v>5</v>
@@ -25473,10 +25357,10 @@
         <v>25</v>
       </c>
       <c r="F653" s="5" t="s">
-        <v>1288</v>
+        <v>1279</v>
       </c>
       <c r="G653" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="654" spans="1:7">
@@ -25484,7 +25368,7 @@
         <v>1211</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C654" s="3" t="s">
         <v>9</v>
@@ -25496,10 +25380,10 @@
         <v>7</v>
       </c>
       <c r="F654" s="5" t="s">
-        <v>1289</v>
+        <v>1280</v>
       </c>
       <c r="G654" t="s">
-        <v>1237</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="655" spans="1:7">
@@ -25507,7 +25391,7 @@
         <v>1211</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C655" s="3" t="s">
         <v>9</v>
@@ -25519,10 +25403,10 @@
         <v>25</v>
       </c>
       <c r="F655" s="5" t="s">
-        <v>1290</v>
+        <v>1281</v>
       </c>
       <c r="G655" t="s">
-        <v>1247</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="656" spans="1:7">
@@ -25530,7 +25414,7 @@
         <v>1211</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C656" s="3" t="s">
         <v>9</v>
@@ -25542,10 +25426,10 @@
         <v>7</v>
       </c>
       <c r="F656" s="5" t="s">
-        <v>1291</v>
+        <v>1282</v>
       </c>
       <c r="G656" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="657" spans="1:7">
@@ -25553,7 +25437,7 @@
         <v>1211</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="C657" s="3" t="s">
         <v>9</v>
@@ -25565,10 +25449,10 @@
         <v>25</v>
       </c>
       <c r="F657" s="5" t="s">
-        <v>1292</v>
+        <v>1283</v>
       </c>
       <c r="G657" t="s">
-        <v>1240</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="658" spans="1:7">
@@ -25588,10 +25472,10 @@
         <v>25</v>
       </c>
       <c r="F658" s="5" t="s">
-        <v>1293</v>
+        <v>1284</v>
       </c>
       <c r="G658" t="s">
-        <v>1249</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="659" spans="1:7">
@@ -25611,10 +25495,10 @@
         <v>7</v>
       </c>
       <c r="F659" s="5" t="s">
-        <v>1294</v>
+        <v>1285</v>
       </c>
       <c r="G659" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="660" spans="1:7">
@@ -25634,10 +25518,10 @@
         <v>7</v>
       </c>
       <c r="F660" s="5" t="s">
-        <v>1295</v>
+        <v>1286</v>
       </c>
       <c r="G660" t="s">
-        <v>1251</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="661" spans="1:7">
@@ -25657,10 +25541,10 @@
         <v>25</v>
       </c>
       <c r="F661" s="5" t="s">
-        <v>1296</v>
+        <v>1287</v>
       </c>
       <c r="G661" t="s">
-        <v>1247</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="662" spans="1:7">
@@ -25680,10 +25564,10 @@
         <v>7</v>
       </c>
       <c r="F662" s="5" t="s">
-        <v>1297</v>
+        <v>1288</v>
       </c>
       <c r="G662" t="s">
-        <v>1251</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="663" spans="1:7">
@@ -25703,10 +25587,10 @@
         <v>25</v>
       </c>
       <c r="F663" s="5" t="s">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="G663" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="664" spans="1:7">
@@ -25726,10 +25610,10 @@
         <v>7</v>
       </c>
       <c r="F664" s="5" t="s">
-        <v>1299</v>
+        <v>1290</v>
       </c>
       <c r="G664" t="s">
-        <v>1252</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="665" spans="1:7">
@@ -25749,10 +25633,1850 @@
         <v>25</v>
       </c>
       <c r="F665" s="5" t="s">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="G665" t="s">
-        <v>1247</v>
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7">
+      <c r="A666" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D666" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E666" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F666" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="667" spans="1:7">
+      <c r="A667" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D667" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E667" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F667" s="5" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7">
+      <c r="A668" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D668" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E668" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F668" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="669" spans="1:7">
+      <c r="A669" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D669" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E669" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F669" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="670" spans="1:7">
+      <c r="A670" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D670" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E670" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F670" s="5" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="671" spans="1:7">
+      <c r="A671" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D671" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E671" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F671" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="672" spans="1:7">
+      <c r="A672" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D672" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E672" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F672" s="5" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7">
+      <c r="A673" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D673" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E673" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F673" s="5" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="674" spans="1:7">
+      <c r="A674" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B674" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C674" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D674" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E674" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F674" s="8" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G674" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7">
+      <c r="A675" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B675" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C675" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D675" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E675" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F675" s="8" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G675" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="676" spans="1:7">
+      <c r="A676" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B676" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C676" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D676" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E676" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F676" s="8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G676" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="677" spans="1:7">
+      <c r="A677" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B677" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C677" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D677" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E677" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F677" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G677" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7">
+      <c r="A678" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B678" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C678" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D678" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E678" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F678" s="8" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G678" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="679" spans="1:7">
+      <c r="A679" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B679" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C679" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D679" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E679" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F679" s="8" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G679" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="680" spans="1:7">
+      <c r="A680" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B680" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C680" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D680" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E680" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F680" s="8" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G680" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="681" spans="1:7">
+      <c r="A681" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B681" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C681" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D681" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E681" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F681" s="8" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G681" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="682" spans="1:7">
+      <c r="A682" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B682" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C682" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D682" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E682" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F682" s="8" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G682" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="683" spans="1:7">
+      <c r="A683" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B683" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C683" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D683" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E683" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F683" s="8" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G683" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="684" spans="1:7">
+      <c r="A684" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B684" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C684" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D684" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E684" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F684" s="8" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G684" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="685" spans="1:7">
+      <c r="A685" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B685" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C685" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D685" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E685" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F685" s="8" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G685" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="686" spans="1:7">
+      <c r="A686" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B686" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C686" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D686" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E686" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F686" s="8" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G686" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="687" spans="1:7">
+      <c r="A687" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B687" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C687" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D687" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E687" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F687" s="8" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G687" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="688" spans="1:7">
+      <c r="A688" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B688" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C688" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D688" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E688" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F688" s="8" t="s">
+        <v>1397</v>
+      </c>
+      <c r="G688" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="689" spans="1:7">
+      <c r="A689" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B689" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C689" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D689" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E689" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F689" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G689" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7">
+      <c r="A690" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B690" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C690" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D690" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E690" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F690" s="8" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G690" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7">
+      <c r="A691" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B691" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C691" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D691" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E691" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F691" s="8" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G691" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7">
+      <c r="A692" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B692" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C692" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D692" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E692" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F692" s="8" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G692" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7">
+      <c r="A693" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B693" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C693" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D693" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E693" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F693" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="G693" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7">
+      <c r="A694" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B694" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C694" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D694" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E694" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F694" s="8" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G694" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7">
+      <c r="A695" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B695" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C695" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D695" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E695" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F695" s="8" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G695" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7">
+      <c r="A696" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B696" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C696" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D696" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E696" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F696" s="8" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G696" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7">
+      <c r="A697" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B697" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C697" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D697" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E697" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F697" s="8" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G697" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7">
+      <c r="A698" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B698" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C698" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D698" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E698" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F698" s="8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G698" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7">
+      <c r="A699" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B699" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C699" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D699" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E699" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F699" s="8" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G699" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7">
+      <c r="A700" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B700" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C700" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D700" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E700" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F700" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G700" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7">
+      <c r="A701" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B701" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C701" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D701" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E701" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F701" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G701" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7">
+      <c r="A702" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B702" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C702" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D702" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E702" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F702" s="8" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G702" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7">
+      <c r="A703" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B703" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C703" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D703" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E703" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F703" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G703" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7">
+      <c r="A704" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B704" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C704" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D704" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E704" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F704" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G704" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7">
+      <c r="A705" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B705" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C705" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D705" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E705" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F705" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G705" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7">
+      <c r="A706" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B706" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C706" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D706" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E706" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F706" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G706" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="707" spans="1:7">
+      <c r="A707" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B707" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C707" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D707" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E707" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F707" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G707" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7">
+      <c r="A708" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B708" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C708" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D708" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E708" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F708" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G708" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="709" spans="1:7">
+      <c r="A709" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B709" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C709" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D709" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E709" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F709" s="8" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G709" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="710" spans="1:7">
+      <c r="A710" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B710" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C710" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D710" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E710" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F710" s="8" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G710" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="711" spans="1:7">
+      <c r="A711" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B711" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C711" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D711" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E711" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F711" s="8" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G711" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="712" spans="1:7">
+      <c r="A712" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B712" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C712" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D712" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E712" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F712" s="8" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G712" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="713" spans="1:7">
+      <c r="A713" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B713" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C713" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D713" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E713" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F713" s="8" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G713" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="714" spans="1:7">
+      <c r="A714" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B714" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C714" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D714" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E714" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F714" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G714" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7">
+      <c r="A715" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B715" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C715" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D715" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E715" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F715" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G715" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="716" spans="1:7">
+      <c r="A716" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B716" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C716" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D716" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E716" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F716" s="8" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G716" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="717" spans="1:7">
+      <c r="A717" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B717" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C717" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D717" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E717" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F717" s="8" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G717" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="718" spans="1:7">
+      <c r="A718" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B718" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C718" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D718" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E718" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F718" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G718" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="719" spans="1:7">
+      <c r="A719" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B719" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C719" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D719" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E719" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F719" s="8" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G719" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="720" spans="1:7">
+      <c r="A720" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B720" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C720" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D720" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E720" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F720" s="8" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G720" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="721" spans="1:7">
+      <c r="A721" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B721" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C721" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D721" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E721" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F721" s="8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G721" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7">
+      <c r="A722" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B722" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C722" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D722" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E722" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F722" s="8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G722" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7">
+      <c r="A723" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B723" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C723" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D723" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E723" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F723" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G723" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7">
+      <c r="A724" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B724" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C724" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D724" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E724" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F724" s="8" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G724" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7">
+      <c r="A725" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B725" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C725" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D725" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E725" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F725" s="8" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G725" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7">
+      <c r="A726" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B726" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C726" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D726" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E726" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F726" s="8" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G726" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7">
+      <c r="A727" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B727" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C727" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D727" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E727" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F727" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G727" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7">
+      <c r="A728" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B728" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C728" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D728" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E728" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F728" s="8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G728" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7">
+      <c r="A729" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B729" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C729" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D729" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E729" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F729" s="8" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G729" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="730" spans="1:7">
+      <c r="A730" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B730" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C730" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D730" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E730" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F730" s="8" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G730" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="731" spans="1:7">
+      <c r="A731" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B731" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C731" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D731" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E731" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F731" s="8" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G731" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="732" spans="1:7">
+      <c r="A732" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B732" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C732" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D732" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E732" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F732" s="8" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G732" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="733" spans="1:7">
+      <c r="A733" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B733" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C733" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D733" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E733" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F733" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G733" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="734" spans="1:7">
+      <c r="A734" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B734" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C734" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D734" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E734" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F734" s="8" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G734" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="735" spans="1:7">
+      <c r="A735" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B735" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C735" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D735" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E735" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F735" s="8" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G735" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="736" spans="1:7">
+      <c r="A736" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B736" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C736" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D736" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E736" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F736" s="8" t="s">
+        <v>1476</v>
+      </c>
+      <c r="G736" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="737" spans="1:7">
+      <c r="A737" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B737" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C737" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D737" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E737" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F737" s="8" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G737" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="738" spans="1:7">
+      <c r="A738" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B738" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C738" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D738" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E738" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F738" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G738" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="739" spans="1:7">
+      <c r="A739" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B739" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C739" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D739" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E739" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F739" s="8" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G739" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="740" spans="1:7">
+      <c r="A740" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B740" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C740" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D740" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E740" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F740" s="8" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G740" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="741" spans="1:7">
+      <c r="A741" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B741" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C741" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D741" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E741" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F741" s="8" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G741" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="742" spans="1:7">
+      <c r="A742" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B742" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C742" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D742" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E742" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F742" s="8" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G742" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="743" spans="1:7">
+      <c r="A743" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B743" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C743" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D743" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E743" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F743" s="8" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G743" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="744" spans="1:7">
+      <c r="A744" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B744" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C744" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D744" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E744" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F744" s="8" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G744" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="745" spans="1:7">
+      <c r="A745" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B745" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C745" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D745" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E745" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F745" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G745" t="s">
+        <v>1406</v>
       </c>
     </row>
   </sheetData>
@@ -25866,1820 +27590,2475 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA84ECF-43D2-4D27-B621-248D16B78DFD}">
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.08984375" customWidth="1"/>
-    <col min="2" max="2" width="70.26953125" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" customWidth="1"/>
     <col min="4" max="4" width="16.90625" customWidth="1"/>
     <col min="5" max="5" width="17.90625" customWidth="1"/>
-    <col min="6" max="6" width="104.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="7" width="40.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="5" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="8"/>
+      <c r="B1" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="8"/>
+      <c r="B2" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>1301</v>
-      </c>
-      <c r="G50" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>1302</v>
-      </c>
-      <c r="G51" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="G52" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="8"/>
+      <c r="B3" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="8"/>
+      <c r="B4" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>1304</v>
-      </c>
-      <c r="G53" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>1305</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="5" t="s">
+      <c r="G4" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="8"/>
+      <c r="B5" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="8"/>
+      <c r="B6" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="G55" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="G56" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="8"/>
+      <c r="B7" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>1308</v>
-      </c>
-      <c r="G57" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>1352</v>
-      </c>
-      <c r="G58" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>1353</v>
-      </c>
-      <c r="G59" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>1354</v>
-      </c>
-      <c r="G60" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G61" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>1356</v>
-      </c>
-      <c r="G62" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>1357</v>
-      </c>
-      <c r="G63" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>1358</v>
-      </c>
-      <c r="G64" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>1359</v>
-      </c>
-      <c r="G65" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G66" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G67" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>1362</v>
       </c>
-      <c r="G68" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69" s="5" t="s">
+      <c r="H8" s="3" t="s">
         <v>1363</v>
       </c>
-      <c r="G69" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" s="5" t="s">
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8" t="s">
         <v>1364</v>
       </c>
-      <c r="G70" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F71" s="5" t="s">
+      <c r="C9" s="8" t="s">
         <v>1365</v>
       </c>
-      <c r="G71" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" s="5" t="s">
+      <c r="D9" s="8" t="s">
         <v>1366</v>
       </c>
-      <c r="G72" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" s="5" t="s">
+      <c r="E9" s="8" t="s">
         <v>1367</v>
       </c>
-      <c r="G73" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F74" s="5" t="s">
+      <c r="F9" s="8" t="s">
         <v>1368</v>
       </c>
-      <c r="G74" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" s="5" t="s">
+      <c r="G9" s="8" t="s">
         <v>1369</v>
       </c>
-      <c r="G75" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="5" t="s">
+      <c r="H9" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>1370</v>
       </c>
-      <c r="G76" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F77" s="5" t="s">
+      <c r="G10" s="8" t="s">
         <v>1371</v>
       </c>
-      <c r="G77" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" s="5" t="s">
+      <c r="H10" t="s">
         <v>1372</v>
       </c>
-      <c r="G78" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" s="5" t="s">
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>1373</v>
       </c>
-      <c r="G79" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" s="5" t="s">
+      <c r="F11" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>1374</v>
       </c>
-      <c r="G80" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" s="5" t="s">
+      <c r="H11" t="s">
         <v>1375</v>
       </c>
-      <c r="G81" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" s="5" t="s">
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="G82" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" s="5" t="s">
+      <c r="H12" t="s">
         <v>1377</v>
       </c>
-      <c r="G83" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" s="5" t="s">
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>1378</v>
       </c>
-      <c r="G84" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F85" s="5" t="s">
+      <c r="E13" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>1379</v>
       </c>
-      <c r="G85" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" s="5" t="s">
+      <c r="H13" t="s">
         <v>1380</v>
       </c>
-      <c r="G86" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F87" s="5" t="s">
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>1381</v>
       </c>
-      <c r="G87" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" s="5" t="s">
+      <c r="H14" t="s">
         <v>1382</v>
       </c>
-      <c r="G88" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F89" s="5" t="s">
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>1383</v>
       </c>
-      <c r="G89" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G90" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G92" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G93" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>1217</v>
-      </c>
-      <c r="G94" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G95" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>1219</v>
-      </c>
-      <c r="G96" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>1220</v>
-      </c>
+      <c r="H15" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H48" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H49" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>1443</v>
+      </c>
+      <c r="H51" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H52" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H62" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>1472</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>1474</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H75" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>1488</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="8"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="8"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="8"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="8"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="8"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="8"/>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="8"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="8"/>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C28FCC-CCA4-402C-8A5B-783E5006D6E1}">
-  <dimension ref="A1:G49"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="33.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1295</v>
+      </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+    <row r="2" spans="1:7" hidden="1">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1297</v>
+      </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="4"/>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+    <row r="3" spans="1:7" hidden="1">
+      <c r="A3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1298</v>
+      </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+    <row r="4" spans="1:7" hidden="1">
+      <c r="A4" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1299</v>
+      </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1301</v>
+      </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1302</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+    <row r="7" spans="1:7" hidden="1">
+      <c r="A7" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1303</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1304</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+    <row r="9" spans="1:7" hidden="1">
+      <c r="A9" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1305</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+    <row r="10" spans="1:7" hidden="1">
+      <c r="A10" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1307</v>
+      </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+    <row r="11" spans="1:7" hidden="1">
+      <c r="A11" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1309</v>
+      </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+    <row r="12" spans="1:7" hidden="1">
+      <c r="A12" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1311</v>
+      </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+    <row r="13" spans="1:7" hidden="1">
+      <c r="A13" s="5" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+    <row r="14" spans="1:7" hidden="1">
+      <c r="A14" s="5" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1315</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+    <row r="15" spans="1:7" hidden="1">
+      <c r="A15" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1317</v>
+      </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+    <row r="16" spans="1:7" hidden="1">
+      <c r="A16" s="5" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1299</v>
+      </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="A17" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1320</v>
+      </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+    <row r="18" spans="1:7" hidden="1">
+      <c r="A18" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1322</v>
+      </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+    <row r="19" spans="1:7" hidden="1">
+      <c r="A19" s="5" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1324</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+    <row r="20" spans="1:7" hidden="1">
+      <c r="A20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1325</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+    <row r="21" spans="1:7" hidden="1">
+      <c r="A21" s="5" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1297</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="A22" s="5" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1304</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="A23" s="5" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1329</v>
+      </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+    <row r="24" spans="1:7" hidden="1">
+      <c r="A24" s="5" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1297</v>
+      </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="3"/>
+      <c r="A25" s="5" t="s">
+        <v>1331</v>
+      </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>1333</v>
+      </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+    <row r="26" spans="1:7" hidden="1">
+      <c r="A26" s="5" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1335</v>
+      </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+    <row r="27" spans="1:7" hidden="1">
+      <c r="A27" s="5" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1324</v>
+      </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+    <row r="28" spans="1:7" hidden="1">
+      <c r="A28" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1338</v>
+      </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+    <row r="29" spans="1:7" hidden="1">
+      <c r="A29" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1338</v>
+      </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="A30" s="5" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1341</v>
+      </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="A31" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1343</v>
+      </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
+      <c r="A32" s="5" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1345</v>
+      </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="4"/>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+    <row r="33" spans="1:7" hidden="1">
+      <c r="A33" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1347</v>
+      </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="4"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -27688,7 +30067,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -27697,7 +30076,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="4"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -27706,7 +30085,7 @@
       <c r="F36" s="5"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -27715,7 +30094,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -27724,7 +30103,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -27733,7 +30112,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -27742,7 +30121,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="4"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -27751,7 +30130,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="4"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -27760,7 +30139,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="4"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -27769,7 +30148,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -27778,7 +30157,7 @@
       <c r="F44" s="5"/>
       <c r="G44" s="4"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -27787,7 +30166,7 @@
       <c r="F45" s="5"/>
       <c r="G45" s="4"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -27796,7 +30175,7 @@
       <c r="F46" s="5"/>
       <c r="G46" s="4"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -27805,7 +30184,7 @@
       <c r="F47" s="5"/>
       <c r="G47" s="4"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -27814,16 +30193,15 @@
       <c r="F48" s="5"/>
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="4"/>
-    </row>
   </sheetData>
+  <autoFilter ref="B1:B48" xr:uid="{A8C28FCC-CCA4-402C-8A5B-783E5006D6E1}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Monoclonal antibody"/>
+        <filter val="Monoclonal antibody*"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>